--- a/whoscored/England3_teams.xlsx
+++ b/whoscored/England3_teams.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Subramanya.Ganti\Downloads\Sports\football\whoscored\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05297E2B-A7D4-4E95-8E77-E3F6D874F4CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0722CCDB-23C0-4BB3-828B-60636FB56936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="119">
   <si>
     <t>team</t>
   </si>
@@ -375,6 +375,15 @@
   <si>
     <t>RC</t>
   </si>
+  <si>
+    <t>Leicester</t>
+  </si>
+  <si>
+    <t>Bromley</t>
+  </si>
+  <si>
+    <t>Notts Co.</t>
+  </si>
 </sst>
 </file>
 
@@ -692,7 +701,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AV168"/>
+  <dimension ref="A1:AV192"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:48" x14ac:dyDescent="0.25">
@@ -25218,6 +25227,3510 @@
       </c>
       <c r="AV168">
         <v>5.4220957420878603E-2</v>
+      </c>
+    </row>
+    <row r="169" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>0</v>
+      </c>
+      <c r="B169" t="s">
+        <v>55</v>
+      </c>
+      <c r="C169">
+        <v>9</v>
+      </c>
+      <c r="D169">
+        <v>0.55555555555555503</v>
+      </c>
+      <c r="E169">
+        <v>0.11111111111111099</v>
+      </c>
+      <c r="F169">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G169">
+        <v>1.7777777777777699</v>
+      </c>
+      <c r="H169">
+        <v>1.2222222222222201</v>
+      </c>
+      <c r="I169">
+        <v>0.55555555555555503</v>
+      </c>
+      <c r="J169">
+        <v>1.7777777777777699</v>
+      </c>
+      <c r="K169">
+        <v>810</v>
+      </c>
+      <c r="L169">
+        <v>436</v>
+      </c>
+      <c r="M169">
+        <v>0.46788990825687998</v>
+      </c>
+      <c r="N169">
+        <v>30</v>
+      </c>
+      <c r="O169">
+        <v>14</v>
+      </c>
+      <c r="P169">
+        <v>58</v>
+      </c>
+      <c r="Q169">
+        <v>14</v>
+      </c>
+      <c r="R169">
+        <v>0</v>
+      </c>
+      <c r="S169">
+        <v>255</v>
+      </c>
+      <c r="T169">
+        <v>51</v>
+      </c>
+      <c r="U169">
+        <v>41</v>
+      </c>
+      <c r="V169">
+        <v>92</v>
+      </c>
+      <c r="W169">
+        <v>0.44565217391304301</v>
+      </c>
+      <c r="X169">
+        <v>94</v>
+      </c>
+      <c r="Y169">
+        <v>116</v>
+      </c>
+      <c r="Z169">
+        <v>73</v>
+      </c>
+      <c r="AA169">
+        <v>2869</v>
+      </c>
+      <c r="AB169">
+        <v>0.320066334991708</v>
+      </c>
+      <c r="AC169">
+        <v>0.77581641659311495</v>
+      </c>
+      <c r="AD169">
+        <v>0.26610767872903701</v>
+      </c>
+      <c r="AE169">
+        <v>78</v>
+      </c>
+      <c r="AF169">
+        <v>163</v>
+      </c>
+      <c r="AG169">
+        <v>76</v>
+      </c>
+      <c r="AH169">
+        <v>31</v>
+      </c>
+      <c r="AI169">
+        <v>16</v>
+      </c>
+      <c r="AJ169">
+        <v>129</v>
+      </c>
+      <c r="AK169">
+        <v>0.34883720930232498</v>
+      </c>
+      <c r="AL169">
+        <v>0.27906976744186002</v>
+      </c>
+      <c r="AM169">
+        <v>213</v>
+      </c>
+      <c r="AN169">
+        <v>0.70892018779342703</v>
+      </c>
+      <c r="AO169" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP169">
+        <v>0.43136863835461597</v>
+      </c>
+      <c r="AQ169">
+        <v>11.8888888888888</v>
+      </c>
+      <c r="AR169">
+        <v>2027</v>
+      </c>
+      <c r="AS169">
+        <v>0.592592592592592</v>
+      </c>
+      <c r="AT169">
+        <v>90</v>
+      </c>
+      <c r="AU169">
+        <v>0.26176962988982699</v>
+      </c>
+      <c r="AV169">
+        <v>0.168441481221284</v>
+      </c>
+    </row>
+    <row r="170" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>1</v>
+      </c>
+      <c r="B170" t="s">
+        <v>51</v>
+      </c>
+      <c r="C170">
+        <v>8</v>
+      </c>
+      <c r="D170">
+        <v>0.625</v>
+      </c>
+      <c r="E170">
+        <v>0.125</v>
+      </c>
+      <c r="F170">
+        <v>0.25</v>
+      </c>
+      <c r="G170">
+        <v>1</v>
+      </c>
+      <c r="H170">
+        <v>0.625</v>
+      </c>
+      <c r="I170">
+        <v>0.375</v>
+      </c>
+      <c r="J170">
+        <v>2</v>
+      </c>
+      <c r="K170">
+        <v>720</v>
+      </c>
+      <c r="L170">
+        <v>434</v>
+      </c>
+      <c r="M170">
+        <v>0.55299539170506895</v>
+      </c>
+      <c r="N170">
+        <v>31</v>
+      </c>
+      <c r="O170">
+        <v>13</v>
+      </c>
+      <c r="P170">
+        <v>54</v>
+      </c>
+      <c r="Q170">
+        <v>19</v>
+      </c>
+      <c r="R170">
+        <v>0</v>
+      </c>
+      <c r="S170">
+        <v>255</v>
+      </c>
+      <c r="T170">
+        <v>37</v>
+      </c>
+      <c r="U170">
+        <v>40</v>
+      </c>
+      <c r="V170">
+        <v>77</v>
+      </c>
+      <c r="W170">
+        <v>0.51948051948051899</v>
+      </c>
+      <c r="X170">
+        <v>103</v>
+      </c>
+      <c r="Y170">
+        <v>125</v>
+      </c>
+      <c r="Z170">
+        <v>69</v>
+      </c>
+      <c r="AA170">
+        <v>2827</v>
+      </c>
+      <c r="AB170">
+        <v>0.33169934640522802</v>
+      </c>
+      <c r="AC170">
+        <v>0.76975169300225699</v>
+      </c>
+      <c r="AD170">
+        <v>0.27629796839729098</v>
+      </c>
+      <c r="AE170">
+        <v>69</v>
+      </c>
+      <c r="AF170">
+        <v>156</v>
+      </c>
+      <c r="AG170">
+        <v>53</v>
+      </c>
+      <c r="AH170">
+        <v>10</v>
+      </c>
+      <c r="AI170">
+        <v>12</v>
+      </c>
+      <c r="AJ170">
+        <v>87</v>
+      </c>
+      <c r="AK170">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="AL170">
+        <v>0.21839080459770099</v>
+      </c>
+      <c r="AM170">
+        <v>189</v>
+      </c>
+      <c r="AN170">
+        <v>0.72486772486772399</v>
+      </c>
+      <c r="AO170" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP170">
+        <v>0.48778391102354302</v>
+      </c>
+      <c r="AQ170">
+        <v>10.25</v>
+      </c>
+      <c r="AR170">
+        <v>2027</v>
+      </c>
+      <c r="AS170">
+        <v>0.70588235294117596</v>
+      </c>
+      <c r="AT170">
+        <v>90</v>
+      </c>
+      <c r="AU170">
+        <v>0.26131732678705699</v>
+      </c>
+      <c r="AV170">
+        <v>0.225157673212942</v>
+      </c>
+    </row>
+    <row r="171" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>2</v>
+      </c>
+      <c r="B171" t="s">
+        <v>56</v>
+      </c>
+      <c r="C171">
+        <v>8</v>
+      </c>
+      <c r="D171">
+        <v>0.5</v>
+      </c>
+      <c r="E171">
+        <v>0.375</v>
+      </c>
+      <c r="F171">
+        <v>0.125</v>
+      </c>
+      <c r="G171">
+        <v>1.75</v>
+      </c>
+      <c r="H171">
+        <v>0.875</v>
+      </c>
+      <c r="I171">
+        <v>0.875</v>
+      </c>
+      <c r="J171">
+        <v>1.875</v>
+      </c>
+      <c r="K171">
+        <v>720</v>
+      </c>
+      <c r="L171">
+        <v>364</v>
+      </c>
+      <c r="M171">
+        <v>0.52747252747252704</v>
+      </c>
+      <c r="N171">
+        <v>19</v>
+      </c>
+      <c r="O171">
+        <v>17</v>
+      </c>
+      <c r="P171">
+        <v>54</v>
+      </c>
+      <c r="Q171">
+        <v>10</v>
+      </c>
+      <c r="R171">
+        <v>1</v>
+      </c>
+      <c r="S171">
+        <v>265</v>
+      </c>
+      <c r="T171">
+        <v>71</v>
+      </c>
+      <c r="U171">
+        <v>42</v>
+      </c>
+      <c r="V171">
+        <v>113</v>
+      </c>
+      <c r="W171">
+        <v>0.37168141592920301</v>
+      </c>
+      <c r="X171">
+        <v>85</v>
+      </c>
+      <c r="Y171">
+        <v>98</v>
+      </c>
+      <c r="Z171">
+        <v>58</v>
+      </c>
+      <c r="AA171">
+        <v>3122</v>
+      </c>
+      <c r="AB171">
+        <v>0.38936170212765903</v>
+      </c>
+      <c r="AC171">
+        <v>0.84049773755656099</v>
+      </c>
+      <c r="AD171">
+        <v>0.177224736048265</v>
+      </c>
+      <c r="AE171">
+        <v>96</v>
+      </c>
+      <c r="AF171">
+        <v>138</v>
+      </c>
+      <c r="AG171">
+        <v>55</v>
+      </c>
+      <c r="AH171">
+        <v>10</v>
+      </c>
+      <c r="AI171">
+        <v>12</v>
+      </c>
+      <c r="AJ171">
+        <v>128</v>
+      </c>
+      <c r="AK171">
+        <v>0.390625</v>
+      </c>
+      <c r="AL171">
+        <v>0.2890625</v>
+      </c>
+      <c r="AM171">
+        <v>148</v>
+      </c>
+      <c r="AN171">
+        <v>0.74324324324324298</v>
+      </c>
+      <c r="AO171" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP171">
+        <v>0.50663449435720398</v>
+      </c>
+      <c r="AQ171">
+        <v>8.375</v>
+      </c>
+      <c r="AR171">
+        <v>2027</v>
+      </c>
+      <c r="AS171">
+        <v>0.63157894736842102</v>
+      </c>
+      <c r="AT171">
+        <v>90</v>
+      </c>
+      <c r="AU171">
+        <v>0.26509204278424903</v>
+      </c>
+      <c r="AV171">
+        <v>0.24018295721575</v>
+      </c>
+    </row>
+    <row r="172" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>3</v>
+      </c>
+      <c r="B172" t="s">
+        <v>86</v>
+      </c>
+      <c r="C172">
+        <v>7</v>
+      </c>
+      <c r="D172">
+        <v>0.57142857142857095</v>
+      </c>
+      <c r="E172">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="F172">
+        <v>0.14285714285714199</v>
+      </c>
+      <c r="G172">
+        <v>1.8571428571428501</v>
+      </c>
+      <c r="H172">
+        <v>0.85714285714285698</v>
+      </c>
+      <c r="I172">
+        <v>1</v>
+      </c>
+      <c r="J172">
+        <v>2</v>
+      </c>
+      <c r="K172">
+        <v>630</v>
+      </c>
+      <c r="L172">
+        <v>259</v>
+      </c>
+      <c r="M172">
+        <v>0.54054054054054002</v>
+      </c>
+      <c r="N172">
+        <v>28</v>
+      </c>
+      <c r="O172">
+        <v>14</v>
+      </c>
+      <c r="P172">
+        <v>44</v>
+      </c>
+      <c r="Q172">
+        <v>14</v>
+      </c>
+      <c r="R172">
+        <v>0</v>
+      </c>
+      <c r="S172">
+        <v>207</v>
+      </c>
+      <c r="T172">
+        <v>60</v>
+      </c>
+      <c r="U172">
+        <v>39</v>
+      </c>
+      <c r="V172">
+        <v>99</v>
+      </c>
+      <c r="W172">
+        <v>0.39393939393939298</v>
+      </c>
+      <c r="X172">
+        <v>73</v>
+      </c>
+      <c r="Y172">
+        <v>90</v>
+      </c>
+      <c r="Z172">
+        <v>61</v>
+      </c>
+      <c r="AA172">
+        <v>2997</v>
+      </c>
+      <c r="AB172">
+        <v>0.34708737864077599</v>
+      </c>
+      <c r="AC172">
+        <v>0.86305609284332596</v>
+      </c>
+      <c r="AD172">
+        <v>0.15938104448742699</v>
+      </c>
+      <c r="AE172">
+        <v>76</v>
+      </c>
+      <c r="AF172">
+        <v>129</v>
+      </c>
+      <c r="AG172">
+        <v>55</v>
+      </c>
+      <c r="AH172">
+        <v>16</v>
+      </c>
+      <c r="AI172">
+        <v>16</v>
+      </c>
+      <c r="AJ172">
+        <v>104</v>
+      </c>
+      <c r="AK172">
+        <v>0.36538461538461497</v>
+      </c>
+      <c r="AL172">
+        <v>0.25961538461538403</v>
+      </c>
+      <c r="AM172">
+        <v>130</v>
+      </c>
+      <c r="AN172">
+        <v>0.79230769230769205</v>
+      </c>
+      <c r="AO172" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP172">
+        <v>0.54026402096936399</v>
+      </c>
+      <c r="AQ172">
+        <v>13.285714285714199</v>
+      </c>
+      <c r="AR172">
+        <v>2027</v>
+      </c>
+      <c r="AS172">
+        <v>0.72727272727272696</v>
+      </c>
+      <c r="AT172">
+        <v>90</v>
+      </c>
+      <c r="AU172">
+        <v>0.26538699997558701</v>
+      </c>
+      <c r="AV172">
+        <v>0.27342728573869801</v>
+      </c>
+    </row>
+    <row r="173" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>4</v>
+      </c>
+      <c r="B173" t="s">
+        <v>50</v>
+      </c>
+      <c r="C173">
+        <v>8</v>
+      </c>
+      <c r="D173">
+        <v>0.5</v>
+      </c>
+      <c r="E173">
+        <v>0.125</v>
+      </c>
+      <c r="F173">
+        <v>0.375</v>
+      </c>
+      <c r="G173">
+        <v>2.125</v>
+      </c>
+      <c r="H173">
+        <v>1.25</v>
+      </c>
+      <c r="I173">
+        <v>0.875</v>
+      </c>
+      <c r="J173">
+        <v>1.625</v>
+      </c>
+      <c r="K173">
+        <v>720</v>
+      </c>
+      <c r="L173">
+        <v>281</v>
+      </c>
+      <c r="M173">
+        <v>0.59074733096085397</v>
+      </c>
+      <c r="N173">
+        <v>18</v>
+      </c>
+      <c r="O173">
+        <v>6</v>
+      </c>
+      <c r="P173">
+        <v>52</v>
+      </c>
+      <c r="Q173">
+        <v>8</v>
+      </c>
+      <c r="R173">
+        <v>0</v>
+      </c>
+      <c r="S173">
+        <v>189</v>
+      </c>
+      <c r="T173">
+        <v>50</v>
+      </c>
+      <c r="U173">
+        <v>58</v>
+      </c>
+      <c r="V173">
+        <v>108</v>
+      </c>
+      <c r="W173">
+        <v>0.53703703703703698</v>
+      </c>
+      <c r="X173">
+        <v>76</v>
+      </c>
+      <c r="Y173">
+        <v>71</v>
+      </c>
+      <c r="Z173">
+        <v>56</v>
+      </c>
+      <c r="AA173">
+        <v>4555</v>
+      </c>
+      <c r="AB173">
+        <v>0.42771084337349302</v>
+      </c>
+      <c r="AC173">
+        <v>0.913975844219866</v>
+      </c>
+      <c r="AD173">
+        <v>0.122750801084545</v>
+      </c>
+      <c r="AE173">
+        <v>104</v>
+      </c>
+      <c r="AF173">
+        <v>142</v>
+      </c>
+      <c r="AG173">
+        <v>78</v>
+      </c>
+      <c r="AH173">
+        <v>17</v>
+      </c>
+      <c r="AI173">
+        <v>18</v>
+      </c>
+      <c r="AJ173">
+        <v>131</v>
+      </c>
+      <c r="AK173">
+        <v>0.32061068702290002</v>
+      </c>
+      <c r="AL173">
+        <v>0.244274809160305</v>
+      </c>
+      <c r="AM173">
+        <v>142</v>
+      </c>
+      <c r="AN173">
+        <v>0.76056338028169002</v>
+      </c>
+      <c r="AO173" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP173">
+        <v>0.58346566180091397</v>
+      </c>
+      <c r="AQ173">
+        <v>9</v>
+      </c>
+      <c r="AR173">
+        <v>2027</v>
+      </c>
+      <c r="AS173">
+        <v>0.64285714285714202</v>
+      </c>
+      <c r="AT173">
+        <v>90</v>
+      </c>
+      <c r="AU173">
+        <v>0.289328704961824</v>
+      </c>
+      <c r="AV173">
+        <v>0.29257129503817503</v>
+      </c>
+    </row>
+    <row r="174" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>5</v>
+      </c>
+      <c r="B174" t="s">
+        <v>77</v>
+      </c>
+      <c r="C174">
+        <v>8</v>
+      </c>
+      <c r="D174">
+        <v>0.375</v>
+      </c>
+      <c r="E174">
+        <v>0.5</v>
+      </c>
+      <c r="F174">
+        <v>0.125</v>
+      </c>
+      <c r="G174">
+        <v>1.625</v>
+      </c>
+      <c r="H174">
+        <v>1.375</v>
+      </c>
+      <c r="I174">
+        <v>0.25</v>
+      </c>
+      <c r="J174">
+        <v>1.625</v>
+      </c>
+      <c r="K174">
+        <v>720</v>
+      </c>
+      <c r="L174">
+        <v>445</v>
+      </c>
+      <c r="M174">
+        <v>0.50337078651685396</v>
+      </c>
+      <c r="N174">
+        <v>22</v>
+      </c>
+      <c r="O174">
+        <v>20</v>
+      </c>
+      <c r="P174">
+        <v>73</v>
+      </c>
+      <c r="Q174">
+        <v>16</v>
+      </c>
+      <c r="R174">
+        <v>0</v>
+      </c>
+      <c r="S174">
+        <v>278</v>
+      </c>
+      <c r="T174">
+        <v>50</v>
+      </c>
+      <c r="U174">
+        <v>32</v>
+      </c>
+      <c r="V174">
+        <v>82</v>
+      </c>
+      <c r="W174">
+        <v>0.39024390243902402</v>
+      </c>
+      <c r="X174">
+        <v>87</v>
+      </c>
+      <c r="Y174">
+        <v>84</v>
+      </c>
+      <c r="Z174">
+        <v>66</v>
+      </c>
+      <c r="AA174">
+        <v>2757</v>
+      </c>
+      <c r="AB174">
+        <v>0.31490787269681703</v>
+      </c>
+      <c r="AC174">
+        <v>0.79768518518518505</v>
+      </c>
+      <c r="AD174">
+        <v>0.27638888888888802</v>
+      </c>
+      <c r="AE174">
+        <v>59</v>
+      </c>
+      <c r="AF174">
+        <v>162</v>
+      </c>
+      <c r="AG174">
+        <v>92</v>
+      </c>
+      <c r="AH174">
+        <v>8</v>
+      </c>
+      <c r="AI174">
+        <v>20</v>
+      </c>
+      <c r="AJ174">
+        <v>96</v>
+      </c>
+      <c r="AK174">
+        <v>0.34375</v>
+      </c>
+      <c r="AL174">
+        <v>0.29166666666666602</v>
+      </c>
+      <c r="AM174">
+        <v>142</v>
+      </c>
+      <c r="AN174">
+        <v>0.75352112676056304</v>
+      </c>
+      <c r="AO174" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP174">
+        <v>0.45883121986612502</v>
+      </c>
+      <c r="AQ174">
+        <v>12.5</v>
+      </c>
+      <c r="AR174">
+        <v>2027</v>
+      </c>
+      <c r="AS174">
+        <v>0.64516129032257996</v>
+      </c>
+      <c r="AT174">
+        <v>90</v>
+      </c>
+      <c r="AU174">
+        <v>0.25954232441838798</v>
+      </c>
+      <c r="AV174">
+        <v>0.198057675581611</v>
+      </c>
+    </row>
+    <row r="175" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>6</v>
+      </c>
+      <c r="B175" t="s">
+        <v>59</v>
+      </c>
+      <c r="C175">
+        <v>8</v>
+      </c>
+      <c r="D175">
+        <v>0.375</v>
+      </c>
+      <c r="E175">
+        <v>0.375</v>
+      </c>
+      <c r="F175">
+        <v>0.25</v>
+      </c>
+      <c r="G175">
+        <v>2.125</v>
+      </c>
+      <c r="H175">
+        <v>1.25</v>
+      </c>
+      <c r="I175">
+        <v>0.875</v>
+      </c>
+      <c r="J175">
+        <v>1.5</v>
+      </c>
+      <c r="K175">
+        <v>720</v>
+      </c>
+      <c r="L175">
+        <v>381</v>
+      </c>
+      <c r="M175">
+        <v>0.54068241469816203</v>
+      </c>
+      <c r="N175">
+        <v>22</v>
+      </c>
+      <c r="O175">
+        <v>9</v>
+      </c>
+      <c r="P175">
+        <v>48</v>
+      </c>
+      <c r="Q175">
+        <v>13</v>
+      </c>
+      <c r="R175">
+        <v>0</v>
+      </c>
+      <c r="S175">
+        <v>271</v>
+      </c>
+      <c r="T175">
+        <v>51</v>
+      </c>
+      <c r="U175">
+        <v>36</v>
+      </c>
+      <c r="V175">
+        <v>87</v>
+      </c>
+      <c r="W175">
+        <v>0.41379310344827502</v>
+      </c>
+      <c r="X175">
+        <v>99</v>
+      </c>
+      <c r="Y175">
+        <v>97</v>
+      </c>
+      <c r="Z175">
+        <v>60</v>
+      </c>
+      <c r="AA175">
+        <v>3013</v>
+      </c>
+      <c r="AB175">
+        <v>0.34313725490196001</v>
+      </c>
+      <c r="AC175">
+        <v>0.84218937275269601</v>
+      </c>
+      <c r="AD175">
+        <v>0.20375549340790999</v>
+      </c>
+      <c r="AE175">
+        <v>99</v>
+      </c>
+      <c r="AF175">
+        <v>141</v>
+      </c>
+      <c r="AG175">
+        <v>70</v>
+      </c>
+      <c r="AH175">
+        <v>24</v>
+      </c>
+      <c r="AI175">
+        <v>16</v>
+      </c>
+      <c r="AJ175">
+        <v>135</v>
+      </c>
+      <c r="AK175">
+        <v>0.31111111111111101</v>
+      </c>
+      <c r="AL175">
+        <v>0.41481481481481403</v>
+      </c>
+      <c r="AM175">
+        <v>109</v>
+      </c>
+      <c r="AN175">
+        <v>0.73394495412843996</v>
+      </c>
+      <c r="AO175" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP175">
+        <v>0.49618144482244803</v>
+      </c>
+      <c r="AQ175">
+        <v>11</v>
+      </c>
+      <c r="AR175">
+        <v>2027</v>
+      </c>
+      <c r="AS175">
+        <v>0.61538461538461497</v>
+      </c>
+      <c r="AT175">
+        <v>90</v>
+      </c>
+      <c r="AU175">
+        <v>0.26469792485017901</v>
+      </c>
+      <c r="AV175">
+        <v>0.23015207514982</v>
+      </c>
+    </row>
+    <row r="176" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>7</v>
+      </c>
+      <c r="B176" t="s">
+        <v>64</v>
+      </c>
+      <c r="C176">
+        <v>9</v>
+      </c>
+      <c r="D176">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E176">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="F176">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G176">
+        <v>1.55555555555555</v>
+      </c>
+      <c r="H176">
+        <v>1.6666666666666601</v>
+      </c>
+      <c r="I176">
+        <v>-0.11111111111111099</v>
+      </c>
+      <c r="J176">
+        <v>1.3333333333333299</v>
+      </c>
+      <c r="K176">
+        <v>810</v>
+      </c>
+      <c r="L176">
+        <v>338</v>
+      </c>
+      <c r="M176">
+        <v>0.523668639053254</v>
+      </c>
+      <c r="N176">
+        <v>34</v>
+      </c>
+      <c r="O176">
+        <v>21</v>
+      </c>
+      <c r="P176">
+        <v>68</v>
+      </c>
+      <c r="Q176">
+        <v>15</v>
+      </c>
+      <c r="R176">
+        <v>1</v>
+      </c>
+      <c r="S176">
+        <v>293</v>
+      </c>
+      <c r="T176">
+        <v>63</v>
+      </c>
+      <c r="U176">
+        <v>53</v>
+      </c>
+      <c r="V176">
+        <v>116</v>
+      </c>
+      <c r="W176">
+        <v>0.45689655172413701</v>
+      </c>
+      <c r="X176">
+        <v>121</v>
+      </c>
+      <c r="Y176">
+        <v>114</v>
+      </c>
+      <c r="Z176">
+        <v>80</v>
+      </c>
+      <c r="AA176">
+        <v>3216</v>
+      </c>
+      <c r="AB176">
+        <v>0.29144851657940601</v>
+      </c>
+      <c r="AC176">
+        <v>0.83049564888384397</v>
+      </c>
+      <c r="AD176">
+        <v>0.21679909194097599</v>
+      </c>
+      <c r="AE176">
+        <v>55</v>
+      </c>
+      <c r="AF176">
+        <v>158</v>
+      </c>
+      <c r="AG176">
+        <v>106</v>
+      </c>
+      <c r="AH176">
+        <v>12</v>
+      </c>
+      <c r="AI176">
+        <v>25</v>
+      </c>
+      <c r="AJ176">
+        <v>82</v>
+      </c>
+      <c r="AK176">
+        <v>0.353658536585365</v>
+      </c>
+      <c r="AL176">
+        <v>0.25609756097560898</v>
+      </c>
+      <c r="AM176">
+        <v>213</v>
+      </c>
+      <c r="AN176">
+        <v>0.79812206572769895</v>
+      </c>
+      <c r="AO176" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP176">
+        <v>0.455678314970484</v>
+      </c>
+      <c r="AQ176">
+        <v>12.8888888888888</v>
+      </c>
+      <c r="AR176">
+        <v>2027</v>
+      </c>
+      <c r="AS176">
+        <v>0.625</v>
+      </c>
+      <c r="AT176">
+        <v>90</v>
+      </c>
+      <c r="AU176">
+        <v>0.26916202909750703</v>
+      </c>
+      <c r="AV176">
+        <v>0.185293526458048</v>
+      </c>
+    </row>
+    <row r="177" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>8</v>
+      </c>
+      <c r="B177" t="s">
+        <v>66</v>
+      </c>
+      <c r="C177">
+        <v>8</v>
+      </c>
+      <c r="D177">
+        <v>0.375</v>
+      </c>
+      <c r="E177">
+        <v>0.375</v>
+      </c>
+      <c r="F177">
+        <v>0.25</v>
+      </c>
+      <c r="G177">
+        <v>0.75</v>
+      </c>
+      <c r="H177">
+        <v>1</v>
+      </c>
+      <c r="I177">
+        <v>-0.25</v>
+      </c>
+      <c r="J177">
+        <v>1.5</v>
+      </c>
+      <c r="K177">
+        <v>720</v>
+      </c>
+      <c r="L177">
+        <v>422</v>
+      </c>
+      <c r="M177">
+        <v>0.523696682464455</v>
+      </c>
+      <c r="N177">
+        <v>30</v>
+      </c>
+      <c r="O177">
+        <v>16</v>
+      </c>
+      <c r="P177">
+        <v>60</v>
+      </c>
+      <c r="Q177">
+        <v>16</v>
+      </c>
+      <c r="R177">
+        <v>0</v>
+      </c>
+      <c r="S177">
+        <v>275</v>
+      </c>
+      <c r="T177">
+        <v>36</v>
+      </c>
+      <c r="U177">
+        <v>25</v>
+      </c>
+      <c r="V177">
+        <v>61</v>
+      </c>
+      <c r="W177">
+        <v>0.40983606557377</v>
+      </c>
+      <c r="X177">
+        <v>84</v>
+      </c>
+      <c r="Y177">
+        <v>99</v>
+      </c>
+      <c r="Z177">
+        <v>62</v>
+      </c>
+      <c r="AA177">
+        <v>2606</v>
+      </c>
+      <c r="AB177">
+        <v>0.31851851851851798</v>
+      </c>
+      <c r="AC177">
+        <v>0.80687318489835402</v>
+      </c>
+      <c r="AD177">
+        <v>0.26137463697967001</v>
+      </c>
+      <c r="AE177">
+        <v>67</v>
+      </c>
+      <c r="AF177">
+        <v>161</v>
+      </c>
+      <c r="AG177">
+        <v>55</v>
+      </c>
+      <c r="AH177">
+        <v>17</v>
+      </c>
+      <c r="AI177">
+        <v>27</v>
+      </c>
+      <c r="AJ177">
+        <v>85</v>
+      </c>
+      <c r="AK177">
+        <v>0.247058823529411</v>
+      </c>
+      <c r="AL177">
+        <v>0.28235294117646997</v>
+      </c>
+      <c r="AM177">
+        <v>162</v>
+      </c>
+      <c r="AN177">
+        <v>0.77160493827160404</v>
+      </c>
+      <c r="AO177" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP177">
+        <v>0.45421884309299598</v>
+      </c>
+      <c r="AQ177">
+        <v>13.5</v>
+      </c>
+      <c r="AR177">
+        <v>2027</v>
+      </c>
+      <c r="AS177">
+        <v>0.77142857142857102</v>
+      </c>
+      <c r="AT177">
+        <v>90</v>
+      </c>
+      <c r="AU177">
+        <v>0.25849078188662999</v>
+      </c>
+      <c r="AV177">
+        <v>0.19450921811336899</v>
+      </c>
+    </row>
+    <row r="178" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>9</v>
+      </c>
+      <c r="B178" t="s">
+        <v>81</v>
+      </c>
+      <c r="C178">
+        <v>6</v>
+      </c>
+      <c r="D178">
+        <v>0.5</v>
+      </c>
+      <c r="E178">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="F178">
+        <v>0.16666666666666599</v>
+      </c>
+      <c r="G178">
+        <v>2.1666666666666599</v>
+      </c>
+      <c r="H178">
+        <v>1.1666666666666601</v>
+      </c>
+      <c r="I178">
+        <v>1</v>
+      </c>
+      <c r="J178">
+        <v>1.8333333333333299</v>
+      </c>
+      <c r="K178">
+        <v>540</v>
+      </c>
+      <c r="L178">
+        <v>215</v>
+      </c>
+      <c r="M178">
+        <v>0.46976744186046498</v>
+      </c>
+      <c r="N178">
+        <v>34</v>
+      </c>
+      <c r="O178">
+        <v>8</v>
+      </c>
+      <c r="P178">
+        <v>39</v>
+      </c>
+      <c r="Q178">
+        <v>11</v>
+      </c>
+      <c r="R178">
+        <v>0</v>
+      </c>
+      <c r="S178">
+        <v>219</v>
+      </c>
+      <c r="T178">
+        <v>58</v>
+      </c>
+      <c r="U178">
+        <v>50</v>
+      </c>
+      <c r="V178">
+        <v>108</v>
+      </c>
+      <c r="W178">
+        <v>0.46296296296296202</v>
+      </c>
+      <c r="X178">
+        <v>86</v>
+      </c>
+      <c r="Y178">
+        <v>91</v>
+      </c>
+      <c r="Z178">
+        <v>54</v>
+      </c>
+      <c r="AA178">
+        <v>2550</v>
+      </c>
+      <c r="AB178">
+        <v>0.36021505376343999</v>
+      </c>
+      <c r="AC178">
+        <v>0.86593204775022903</v>
+      </c>
+      <c r="AD178">
+        <v>0.17079889807162499</v>
+      </c>
+      <c r="AE178">
+        <v>54</v>
+      </c>
+      <c r="AF178">
+        <v>109</v>
+      </c>
+      <c r="AG178">
+        <v>71</v>
+      </c>
+      <c r="AH178">
+        <v>6</v>
+      </c>
+      <c r="AI178">
+        <v>16</v>
+      </c>
+      <c r="AJ178">
+        <v>67</v>
+      </c>
+      <c r="AK178">
+        <v>0.402985074626865</v>
+      </c>
+      <c r="AL178">
+        <v>0.35820895522388002</v>
+      </c>
+      <c r="AM178">
+        <v>142</v>
+      </c>
+      <c r="AN178">
+        <v>0.79577464788732399</v>
+      </c>
+      <c r="AO178" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP178">
+        <v>0.57751636422397901</v>
+      </c>
+      <c r="AQ178">
+        <v>17</v>
+      </c>
+      <c r="AR178">
+        <v>2027</v>
+      </c>
+      <c r="AS178">
+        <v>0.69565217391304301</v>
+      </c>
+      <c r="AT178">
+        <v>90</v>
+      </c>
+      <c r="AU178">
+        <v>0.25589224621582302</v>
+      </c>
+      <c r="AV178">
+        <v>0.320074420450842</v>
+      </c>
+    </row>
+    <row r="179" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>10</v>
+      </c>
+      <c r="B179" t="s">
+        <v>67</v>
+      </c>
+      <c r="C179">
+        <v>8</v>
+      </c>
+      <c r="D179">
+        <v>0.375</v>
+      </c>
+      <c r="E179">
+        <v>0.125</v>
+      </c>
+      <c r="F179">
+        <v>0.5</v>
+      </c>
+      <c r="G179">
+        <v>1.625</v>
+      </c>
+      <c r="H179">
+        <v>1.375</v>
+      </c>
+      <c r="I179">
+        <v>0.25</v>
+      </c>
+      <c r="J179">
+        <v>1.25</v>
+      </c>
+      <c r="K179">
+        <v>720</v>
+      </c>
+      <c r="L179">
+        <v>436</v>
+      </c>
+      <c r="M179">
+        <v>0.46788990825687998</v>
+      </c>
+      <c r="N179">
+        <v>38</v>
+      </c>
+      <c r="O179">
+        <v>13</v>
+      </c>
+      <c r="P179">
+        <v>78</v>
+      </c>
+      <c r="Q179">
+        <v>18</v>
+      </c>
+      <c r="R179">
+        <v>0</v>
+      </c>
+      <c r="S179">
+        <v>284</v>
+      </c>
+      <c r="T179">
+        <v>66</v>
+      </c>
+      <c r="U179">
+        <v>45</v>
+      </c>
+      <c r="V179">
+        <v>111</v>
+      </c>
+      <c r="W179">
+        <v>0.40540540540540498</v>
+      </c>
+      <c r="X179">
+        <v>107</v>
+      </c>
+      <c r="Y179">
+        <v>99</v>
+      </c>
+      <c r="Z179">
+        <v>59</v>
+      </c>
+      <c r="AA179">
+        <v>2942</v>
+      </c>
+      <c r="AB179">
+        <v>0.235067437379576</v>
+      </c>
+      <c r="AC179">
+        <v>0.80891456871646705</v>
+      </c>
+      <c r="AD179">
+        <v>0.21419727610400299</v>
+      </c>
+      <c r="AE179">
+        <v>60</v>
+      </c>
+      <c r="AF179">
+        <v>163</v>
+      </c>
+      <c r="AG179">
+        <v>70</v>
+      </c>
+      <c r="AH179">
+        <v>9</v>
+      </c>
+      <c r="AI179">
+        <v>29</v>
+      </c>
+      <c r="AJ179">
+        <v>83</v>
+      </c>
+      <c r="AK179">
+        <v>0.38554216867469798</v>
+      </c>
+      <c r="AL179">
+        <v>0.19277108433734899</v>
+      </c>
+      <c r="AM179">
+        <v>185</v>
+      </c>
+      <c r="AN179">
+        <v>0.72432432432432403</v>
+      </c>
+      <c r="AO179" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP179">
+        <v>0.50535606383856502</v>
+      </c>
+      <c r="AQ179">
+        <v>15.875</v>
+      </c>
+      <c r="AR179">
+        <v>2027</v>
+      </c>
+      <c r="AS179">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="AT179">
+        <v>90</v>
+      </c>
+      <c r="AU179">
+        <v>0.268408417730372</v>
+      </c>
+      <c r="AV179">
+        <v>0.23559158226962701</v>
+      </c>
+    </row>
+    <row r="180" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>11</v>
+      </c>
+      <c r="B180" t="s">
+        <v>58</v>
+      </c>
+      <c r="C180">
+        <v>8</v>
+      </c>
+      <c r="D180">
+        <v>0.25</v>
+      </c>
+      <c r="E180">
+        <v>0.5</v>
+      </c>
+      <c r="F180">
+        <v>0.25</v>
+      </c>
+      <c r="G180">
+        <v>1.625</v>
+      </c>
+      <c r="H180">
+        <v>2</v>
+      </c>
+      <c r="I180">
+        <v>-0.375</v>
+      </c>
+      <c r="J180">
+        <v>1.25</v>
+      </c>
+      <c r="K180">
+        <v>720</v>
+      </c>
+      <c r="L180">
+        <v>375</v>
+      </c>
+      <c r="M180">
+        <v>0.54400000000000004</v>
+      </c>
+      <c r="N180">
+        <v>34</v>
+      </c>
+      <c r="O180">
+        <v>8</v>
+      </c>
+      <c r="P180">
+        <v>34</v>
+      </c>
+      <c r="Q180">
+        <v>11</v>
+      </c>
+      <c r="R180">
+        <v>0</v>
+      </c>
+      <c r="S180">
+        <v>308</v>
+      </c>
+      <c r="T180">
+        <v>48</v>
+      </c>
+      <c r="U180">
+        <v>34</v>
+      </c>
+      <c r="V180">
+        <v>82</v>
+      </c>
+      <c r="W180">
+        <v>0.41463414634146301</v>
+      </c>
+      <c r="X180">
+        <v>100</v>
+      </c>
+      <c r="Y180">
+        <v>80</v>
+      </c>
+      <c r="Z180">
+        <v>70</v>
+      </c>
+      <c r="AA180">
+        <v>3059</v>
+      </c>
+      <c r="AB180">
+        <v>0.394495412844036</v>
+      </c>
+      <c r="AC180">
+        <v>0.83651551312649097</v>
+      </c>
+      <c r="AD180">
+        <v>0.21678599840891</v>
+      </c>
+      <c r="AE180">
+        <v>80</v>
+      </c>
+      <c r="AF180">
+        <v>146</v>
+      </c>
+      <c r="AG180">
+        <v>62</v>
+      </c>
+      <c r="AH180">
+        <v>17</v>
+      </c>
+      <c r="AI180">
+        <v>26</v>
+      </c>
+      <c r="AJ180">
+        <v>101</v>
+      </c>
+      <c r="AK180">
+        <v>0.396039603960396</v>
+      </c>
+      <c r="AL180">
+        <v>0.287128712871287</v>
+      </c>
+      <c r="AM180">
+        <v>132</v>
+      </c>
+      <c r="AN180">
+        <v>0.71212121212121204</v>
+      </c>
+      <c r="AO180" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP180">
+        <v>0.49148133262156801</v>
+      </c>
+      <c r="AQ180">
+        <v>15.25</v>
+      </c>
+      <c r="AR180">
+        <v>2027</v>
+      </c>
+      <c r="AS180">
+        <v>0.61904761904761896</v>
+      </c>
+      <c r="AT180">
+        <v>90</v>
+      </c>
+      <c r="AU180">
+        <v>0.26312927833636202</v>
+      </c>
+      <c r="AV180">
+        <v>0.22703322166363701</v>
+      </c>
+    </row>
+    <row r="181" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>12</v>
+      </c>
+      <c r="B181" t="s">
+        <v>53</v>
+      </c>
+      <c r="C181">
+        <v>7</v>
+      </c>
+      <c r="D181">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="E181">
+        <v>0.42857142857142799</v>
+      </c>
+      <c r="F181">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="G181">
+        <v>1.5714285714285701</v>
+      </c>
+      <c r="H181">
+        <v>1.1428571428571399</v>
+      </c>
+      <c r="I181">
+        <v>0.42857142857142799</v>
+      </c>
+      <c r="J181">
+        <v>1.28571428571428</v>
+      </c>
+      <c r="K181">
+        <v>630</v>
+      </c>
+      <c r="L181">
+        <v>334</v>
+      </c>
+      <c r="M181">
+        <v>0.56886227544910095</v>
+      </c>
+      <c r="N181">
+        <v>30</v>
+      </c>
+      <c r="O181">
+        <v>18</v>
+      </c>
+      <c r="P181">
+        <v>56</v>
+      </c>
+      <c r="Q181">
+        <v>14</v>
+      </c>
+      <c r="R181">
+        <v>0</v>
+      </c>
+      <c r="S181">
+        <v>234</v>
+      </c>
+      <c r="T181">
+        <v>35</v>
+      </c>
+      <c r="U181">
+        <v>37</v>
+      </c>
+      <c r="V181">
+        <v>72</v>
+      </c>
+      <c r="W181">
+        <v>0.51388888888888795</v>
+      </c>
+      <c r="X181">
+        <v>96</v>
+      </c>
+      <c r="Y181">
+        <v>97</v>
+      </c>
+      <c r="Z181">
+        <v>62</v>
+      </c>
+      <c r="AA181">
+        <v>2272</v>
+      </c>
+      <c r="AB181">
+        <v>0.35427574171029602</v>
+      </c>
+      <c r="AC181">
+        <v>0.77221895232489701</v>
+      </c>
+      <c r="AD181">
+        <v>0.33725721012360199</v>
+      </c>
+      <c r="AE181">
+        <v>58</v>
+      </c>
+      <c r="AF181">
+        <v>130</v>
+      </c>
+      <c r="AG181">
+        <v>59</v>
+      </c>
+      <c r="AH181">
+        <v>14</v>
+      </c>
+      <c r="AI181">
+        <v>9</v>
+      </c>
+      <c r="AJ181">
+        <v>74</v>
+      </c>
+      <c r="AK181">
+        <v>0.36486486486486402</v>
+      </c>
+      <c r="AL181">
+        <v>0.24324324324324301</v>
+      </c>
+      <c r="AM181">
+        <v>177</v>
+      </c>
+      <c r="AN181">
+        <v>0.80790960451977401</v>
+      </c>
+      <c r="AO181" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP181">
+        <v>0.43395016876386999</v>
+      </c>
+      <c r="AQ181">
+        <v>11</v>
+      </c>
+      <c r="AR181">
+        <v>2027</v>
+      </c>
+      <c r="AS181">
+        <v>0.52941176470588203</v>
+      </c>
+      <c r="AT181">
+        <v>90</v>
+      </c>
+      <c r="AU181">
+        <v>0.24959236789673001</v>
+      </c>
+      <c r="AV181">
+        <v>0.18319334638898399</v>
+      </c>
+    </row>
+    <row r="182" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>13</v>
+      </c>
+      <c r="B182" t="s">
+        <v>116</v>
+      </c>
+      <c r="C182">
+        <v>7</v>
+      </c>
+      <c r="D182">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="E182">
+        <v>0.42857142857142799</v>
+      </c>
+      <c r="F182">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="G182">
+        <v>1.28571428571428</v>
+      </c>
+      <c r="H182">
+        <v>1.5714285714285701</v>
+      </c>
+      <c r="I182">
+        <v>-0.28571428571428498</v>
+      </c>
+      <c r="J182">
+        <v>1.28571428571428</v>
+      </c>
+      <c r="K182">
+        <v>630</v>
+      </c>
+      <c r="L182">
+        <v>164</v>
+      </c>
+      <c r="M182">
+        <v>0.48170731707316999</v>
+      </c>
+      <c r="N182">
+        <v>14</v>
+      </c>
+      <c r="O182">
+        <v>16</v>
+      </c>
+      <c r="P182">
+        <v>52</v>
+      </c>
+      <c r="Q182">
+        <v>14</v>
+      </c>
+      <c r="R182">
+        <v>1</v>
+      </c>
+      <c r="S182">
+        <v>162</v>
+      </c>
+      <c r="T182">
+        <v>54</v>
+      </c>
+      <c r="U182">
+        <v>63</v>
+      </c>
+      <c r="V182">
+        <v>117</v>
+      </c>
+      <c r="W182">
+        <v>0.53846153846153799</v>
+      </c>
+      <c r="X182">
+        <v>101</v>
+      </c>
+      <c r="Y182">
+        <v>68</v>
+      </c>
+      <c r="Z182">
+        <v>37</v>
+      </c>
+      <c r="AA182">
+        <v>4284</v>
+      </c>
+      <c r="AB182">
+        <v>0.352727272727272</v>
+      </c>
+      <c r="AC182">
+        <v>0.90646046395609803</v>
+      </c>
+      <c r="AD182">
+        <v>6.8595659765527506E-2</v>
+      </c>
+      <c r="AE182">
+        <v>79</v>
+      </c>
+      <c r="AF182">
+        <v>124</v>
+      </c>
+      <c r="AG182">
+        <v>80</v>
+      </c>
+      <c r="AH182">
+        <v>8</v>
+      </c>
+      <c r="AI182">
+        <v>18</v>
+      </c>
+      <c r="AJ182">
+        <v>107</v>
+      </c>
+      <c r="AK182">
+        <v>0.32710280373831702</v>
+      </c>
+      <c r="AL182">
+        <v>0.27102803738317699</v>
+      </c>
+      <c r="AM182">
+        <v>128</v>
+      </c>
+      <c r="AN182">
+        <v>0.7109375</v>
+      </c>
+      <c r="AO182" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP182">
+        <v>0.67562725235469401</v>
+      </c>
+      <c r="AQ182">
+        <v>13.1428571428571</v>
+      </c>
+      <c r="AR182">
+        <v>2027</v>
+      </c>
+      <c r="AS182">
+        <v>0.62068965517241304</v>
+      </c>
+      <c r="AT182">
+        <v>90</v>
+      </c>
+      <c r="AU182">
+        <v>0.28831249641941897</v>
+      </c>
+      <c r="AV182">
+        <v>0.385501789294865</v>
+      </c>
+    </row>
+    <row r="183" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>14</v>
+      </c>
+      <c r="B183" t="s">
+        <v>60</v>
+      </c>
+      <c r="C183">
+        <v>7</v>
+      </c>
+      <c r="D183">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="E183">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="F183">
+        <v>0.42857142857142799</v>
+      </c>
+      <c r="G183">
+        <v>1.8571428571428501</v>
+      </c>
+      <c r="H183">
+        <v>1.8571428571428501</v>
+      </c>
+      <c r="I183">
+        <v>0</v>
+      </c>
+      <c r="J183">
+        <v>1.1428571428571399</v>
+      </c>
+      <c r="K183">
+        <v>630</v>
+      </c>
+      <c r="L183">
+        <v>315</v>
+      </c>
+      <c r="M183">
+        <v>0.49523809523809498</v>
+      </c>
+      <c r="N183">
+        <v>37</v>
+      </c>
+      <c r="O183">
+        <v>19</v>
+      </c>
+      <c r="P183">
+        <v>63</v>
+      </c>
+      <c r="Q183">
+        <v>11</v>
+      </c>
+      <c r="R183">
+        <v>0</v>
+      </c>
+      <c r="S183">
+        <v>234</v>
+      </c>
+      <c r="T183">
+        <v>46</v>
+      </c>
+      <c r="U183">
+        <v>39</v>
+      </c>
+      <c r="V183">
+        <v>85</v>
+      </c>
+      <c r="W183">
+        <v>0.45882352941176402</v>
+      </c>
+      <c r="X183">
+        <v>73</v>
+      </c>
+      <c r="Y183">
+        <v>76</v>
+      </c>
+      <c r="Z183">
+        <v>50</v>
+      </c>
+      <c r="AA183">
+        <v>2647</v>
+      </c>
+      <c r="AB183">
+        <v>0.2890625</v>
+      </c>
+      <c r="AC183">
+        <v>0.83747072599531602</v>
+      </c>
+      <c r="AD183">
+        <v>0.239812646370023</v>
+      </c>
+      <c r="AE183">
+        <v>70</v>
+      </c>
+      <c r="AF183">
+        <v>130</v>
+      </c>
+      <c r="AG183">
+        <v>63</v>
+      </c>
+      <c r="AH183">
+        <v>16</v>
+      </c>
+      <c r="AI183">
+        <v>33</v>
+      </c>
+      <c r="AJ183">
+        <v>100</v>
+      </c>
+      <c r="AK183">
+        <v>0.34</v>
+      </c>
+      <c r="AL183">
+        <v>0.23</v>
+      </c>
+      <c r="AM183">
+        <v>174</v>
+      </c>
+      <c r="AN183">
+        <v>0.72988505747126398</v>
+      </c>
+      <c r="AO183" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP183">
+        <v>0.483669298513973</v>
+      </c>
+      <c r="AQ183">
+        <v>19</v>
+      </c>
+      <c r="AR183">
+        <v>2027</v>
+      </c>
+      <c r="AS183">
+        <v>0.71739130434782605</v>
+      </c>
+      <c r="AT183">
+        <v>90</v>
+      </c>
+      <c r="AU183">
+        <v>0.26090700196135802</v>
+      </c>
+      <c r="AV183">
+        <v>0.22146442661006999</v>
+      </c>
+    </row>
+    <row r="184" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>54</v>
+      </c>
+      <c r="C184">
+        <v>7</v>
+      </c>
+      <c r="D184">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="E184">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="F184">
+        <v>0.42857142857142799</v>
+      </c>
+      <c r="G184">
+        <v>1.71428571428571</v>
+      </c>
+      <c r="H184">
+        <v>2</v>
+      </c>
+      <c r="I184">
+        <v>-0.28571428571428498</v>
+      </c>
+      <c r="J184">
+        <v>1.1428571428571399</v>
+      </c>
+      <c r="K184">
+        <v>630</v>
+      </c>
+      <c r="L184">
+        <v>259</v>
+      </c>
+      <c r="M184">
+        <v>0.45559845559845502</v>
+      </c>
+      <c r="N184">
+        <v>26</v>
+      </c>
+      <c r="O184">
+        <v>12</v>
+      </c>
+      <c r="P184">
+        <v>52</v>
+      </c>
+      <c r="Q184">
+        <v>15</v>
+      </c>
+      <c r="R184">
+        <v>1</v>
+      </c>
+      <c r="S184">
+        <v>253</v>
+      </c>
+      <c r="T184">
+        <v>74</v>
+      </c>
+      <c r="U184">
+        <v>47</v>
+      </c>
+      <c r="V184">
+        <v>121</v>
+      </c>
+      <c r="W184">
+        <v>0.38842975206611502</v>
+      </c>
+      <c r="X184">
+        <v>93</v>
+      </c>
+      <c r="Y184">
+        <v>82</v>
+      </c>
+      <c r="Z184">
+        <v>56</v>
+      </c>
+      <c r="AA184">
+        <v>3303</v>
+      </c>
+      <c r="AB184">
+        <v>0.32383419689119097</v>
+      </c>
+      <c r="AC184">
+        <v>0.88207062050051399</v>
+      </c>
+      <c r="AD184">
+        <v>0.13232773397326</v>
+      </c>
+      <c r="AE184">
+        <v>66</v>
+      </c>
+      <c r="AF184">
+        <v>103</v>
+      </c>
+      <c r="AG184">
+        <v>63</v>
+      </c>
+      <c r="AH184">
+        <v>9</v>
+      </c>
+      <c r="AI184">
+        <v>11</v>
+      </c>
+      <c r="AJ184">
+        <v>94</v>
+      </c>
+      <c r="AK184">
+        <v>0.329787234042553</v>
+      </c>
+      <c r="AL184">
+        <v>0.340425531914893</v>
+      </c>
+      <c r="AM184">
+        <v>122</v>
+      </c>
+      <c r="AN184">
+        <v>0.76229508196721296</v>
+      </c>
+      <c r="AO184" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP184">
+        <v>0.56851124766691596</v>
+      </c>
+      <c r="AQ184">
+        <v>10.714285714285699</v>
+      </c>
+      <c r="AR184">
+        <v>2027</v>
+      </c>
+      <c r="AS184">
+        <v>0.44</v>
+      </c>
+      <c r="AT184">
+        <v>90</v>
+      </c>
+      <c r="AU184">
+        <v>0.27214757152248398</v>
+      </c>
+      <c r="AV184">
+        <v>0.29483814276322901</v>
+      </c>
+    </row>
+    <row r="185" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>16</v>
+      </c>
+      <c r="B185" t="s">
+        <v>57</v>
+      </c>
+      <c r="C185">
+        <v>7</v>
+      </c>
+      <c r="D185">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="E185">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="F185">
+        <v>0.42857142857142799</v>
+      </c>
+      <c r="G185">
+        <v>1.4285714285714199</v>
+      </c>
+      <c r="H185">
+        <v>1.8571428571428501</v>
+      </c>
+      <c r="I185">
+        <v>-0.42857142857142799</v>
+      </c>
+      <c r="J185">
+        <v>1.1428571428571399</v>
+      </c>
+      <c r="K185">
+        <v>630</v>
+      </c>
+      <c r="L185">
+        <v>270</v>
+      </c>
+      <c r="M185">
+        <v>0.54444444444444395</v>
+      </c>
+      <c r="N185">
+        <v>24</v>
+      </c>
+      <c r="O185">
+        <v>15</v>
+      </c>
+      <c r="P185">
+        <v>46</v>
+      </c>
+      <c r="Q185">
+        <v>16</v>
+      </c>
+      <c r="R185">
+        <v>1</v>
+      </c>
+      <c r="S185">
+        <v>234</v>
+      </c>
+      <c r="T185">
+        <v>47</v>
+      </c>
+      <c r="U185">
+        <v>42</v>
+      </c>
+      <c r="V185">
+        <v>89</v>
+      </c>
+      <c r="W185">
+        <v>0.47191011235954999</v>
+      </c>
+      <c r="X185">
+        <v>82</v>
+      </c>
+      <c r="Y185">
+        <v>99</v>
+      </c>
+      <c r="Z185">
+        <v>73</v>
+      </c>
+      <c r="AA185">
+        <v>2522</v>
+      </c>
+      <c r="AB185">
+        <v>0.37837837837837801</v>
+      </c>
+      <c r="AC185">
+        <v>0.821166095051445</v>
+      </c>
+      <c r="AD185">
+        <v>0.23566878980891701</v>
+      </c>
+      <c r="AE185">
+        <v>60</v>
+      </c>
+      <c r="AF185">
+        <v>134</v>
+      </c>
+      <c r="AG185">
+        <v>62</v>
+      </c>
+      <c r="AH185">
+        <v>13</v>
+      </c>
+      <c r="AI185">
+        <v>19</v>
+      </c>
+      <c r="AJ185">
+        <v>83</v>
+      </c>
+      <c r="AK185">
+        <v>0.32530120481927699</v>
+      </c>
+      <c r="AL185">
+        <v>0.25301204819277101</v>
+      </c>
+      <c r="AM185">
+        <v>162</v>
+      </c>
+      <c r="AN185">
+        <v>0.70370370370370305</v>
+      </c>
+      <c r="AO185" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP185">
+        <v>0.46033525577040701</v>
+      </c>
+      <c r="AQ185">
+        <v>13.5714285714285</v>
+      </c>
+      <c r="AR185">
+        <v>2027</v>
+      </c>
+      <c r="AS185">
+        <v>0.59375</v>
+      </c>
+      <c r="AT185">
+        <v>90</v>
+      </c>
+      <c r="AU185">
+        <v>0.25392601784233998</v>
+      </c>
+      <c r="AV185">
+        <v>0.205173982157659</v>
+      </c>
+    </row>
+    <row r="186" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>17</v>
+      </c>
+      <c r="B186" t="s">
+        <v>62</v>
+      </c>
+      <c r="C186">
+        <v>7</v>
+      </c>
+      <c r="D186">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="E186">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="F186">
+        <v>0.42857142857142799</v>
+      </c>
+      <c r="G186">
+        <v>1</v>
+      </c>
+      <c r="H186">
+        <v>1.71428571428571</v>
+      </c>
+      <c r="I186">
+        <v>-0.71428571428571397</v>
+      </c>
+      <c r="J186">
+        <v>1.1428571428571399</v>
+      </c>
+      <c r="K186">
+        <v>630</v>
+      </c>
+      <c r="L186">
+        <v>272</v>
+      </c>
+      <c r="M186">
+        <v>0.433823529411764</v>
+      </c>
+      <c r="N186">
+        <v>23</v>
+      </c>
+      <c r="O186">
+        <v>12</v>
+      </c>
+      <c r="P186">
+        <v>45</v>
+      </c>
+      <c r="Q186">
+        <v>18</v>
+      </c>
+      <c r="R186">
+        <v>1</v>
+      </c>
+      <c r="S186">
+        <v>195</v>
+      </c>
+      <c r="T186">
+        <v>74</v>
+      </c>
+      <c r="U186">
+        <v>55</v>
+      </c>
+      <c r="V186">
+        <v>129</v>
+      </c>
+      <c r="W186">
+        <v>0.42635658914728602</v>
+      </c>
+      <c r="X186">
+        <v>74</v>
+      </c>
+      <c r="Y186">
+        <v>95</v>
+      </c>
+      <c r="Z186">
+        <v>62</v>
+      </c>
+      <c r="AA186">
+        <v>2412</v>
+      </c>
+      <c r="AB186">
+        <v>0.30801687763712998</v>
+      </c>
+      <c r="AC186">
+        <v>0.804953560371517</v>
+      </c>
+      <c r="AD186">
+        <v>0.24458204334365299</v>
+      </c>
+      <c r="AE186">
+        <v>72</v>
+      </c>
+      <c r="AF186">
+        <v>165</v>
+      </c>
+      <c r="AG186">
+        <v>83</v>
+      </c>
+      <c r="AH186">
+        <v>17</v>
+      </c>
+      <c r="AI186">
+        <v>16</v>
+      </c>
+      <c r="AJ186">
+        <v>118</v>
+      </c>
+      <c r="AK186">
+        <v>0.25423728813559299</v>
+      </c>
+      <c r="AL186">
+        <v>0.34745762711864397</v>
+      </c>
+      <c r="AM186">
+        <v>150</v>
+      </c>
+      <c r="AN186">
+        <v>0.65333333333333299</v>
+      </c>
+      <c r="AO186" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP186">
+        <v>0.52962117642763895</v>
+      </c>
+      <c r="AQ186">
+        <v>12.5714285714285</v>
+      </c>
+      <c r="AR186">
+        <v>2027</v>
+      </c>
+      <c r="AS186">
+        <v>0.57142857142857095</v>
+      </c>
+      <c r="AT186">
+        <v>90</v>
+      </c>
+      <c r="AU186">
+        <v>0.25430869527765798</v>
+      </c>
+      <c r="AV186">
+        <v>0.27389130472234102</v>
+      </c>
+    </row>
+    <row r="187" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>18</v>
+      </c>
+      <c r="B187" t="s">
+        <v>117</v>
+      </c>
+      <c r="C187">
+        <v>7</v>
+      </c>
+      <c r="D187">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="E187">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="F187">
+        <v>0.42857142857142799</v>
+      </c>
+      <c r="G187">
+        <v>1.1428571428571399</v>
+      </c>
+      <c r="H187">
+        <v>2.5714285714285698</v>
+      </c>
+      <c r="I187">
+        <v>-1.4285714285714199</v>
+      </c>
+      <c r="J187">
+        <v>1.1428571428571399</v>
+      </c>
+      <c r="K187">
+        <v>630</v>
+      </c>
+      <c r="L187">
+        <v>359</v>
+      </c>
+      <c r="M187">
+        <v>0.45403899721448399</v>
+      </c>
+      <c r="N187">
+        <v>25</v>
+      </c>
+      <c r="O187">
+        <v>22</v>
+      </c>
+      <c r="P187">
+        <v>73</v>
+      </c>
+      <c r="Q187">
+        <v>12</v>
+      </c>
+      <c r="R187">
+        <v>0</v>
+      </c>
+      <c r="S187">
+        <v>252</v>
+      </c>
+      <c r="T187">
+        <v>46</v>
+      </c>
+      <c r="U187">
+        <v>20</v>
+      </c>
+      <c r="V187">
+        <v>66</v>
+      </c>
+      <c r="W187">
+        <v>0.30303030303030298</v>
+      </c>
+      <c r="X187">
+        <v>80</v>
+      </c>
+      <c r="Y187">
+        <v>107</v>
+      </c>
+      <c r="Z187">
+        <v>76</v>
+      </c>
+      <c r="AA187">
+        <v>1684</v>
+      </c>
+      <c r="AB187">
+        <v>0.30916030534351102</v>
+      </c>
+      <c r="AC187">
+        <v>0.71379310344827496</v>
+      </c>
+      <c r="AD187">
+        <v>0.451724137931034</v>
+      </c>
+      <c r="AE187">
+        <v>39</v>
+      </c>
+      <c r="AF187">
+        <v>133</v>
+      </c>
+      <c r="AG187">
+        <v>36</v>
+      </c>
+      <c r="AH187">
+        <v>10</v>
+      </c>
+      <c r="AI187">
+        <v>38</v>
+      </c>
+      <c r="AJ187">
+        <v>66</v>
+      </c>
+      <c r="AK187">
+        <v>0.37878787878787801</v>
+      </c>
+      <c r="AL187">
+        <v>0.18181818181818099</v>
+      </c>
+      <c r="AM187">
+        <v>174</v>
+      </c>
+      <c r="AN187">
+        <v>0.77586206896551702</v>
+      </c>
+      <c r="AO187" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP187">
+        <v>0.35820405579396197</v>
+      </c>
+      <c r="AQ187">
+        <v>17.714285714285701</v>
+      </c>
+      <c r="AR187">
+        <v>2027</v>
+      </c>
+      <c r="AS187">
+        <v>0.67857142857142805</v>
+      </c>
+      <c r="AT187">
+        <v>90</v>
+      </c>
+      <c r="AU187">
+        <v>0.24091805201368699</v>
+      </c>
+      <c r="AV187">
+        <v>0.116324805129169</v>
+      </c>
+    </row>
+    <row r="188" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>19</v>
+      </c>
+      <c r="B188" t="s">
+        <v>118</v>
+      </c>
+      <c r="C188">
+        <v>7</v>
+      </c>
+      <c r="D188">
+        <v>0.14285714285714199</v>
+      </c>
+      <c r="E188">
+        <v>0.57142857142857095</v>
+      </c>
+      <c r="F188">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="G188">
+        <v>1</v>
+      </c>
+      <c r="H188">
+        <v>1.28571428571428</v>
+      </c>
+      <c r="I188">
+        <v>-0.28571428571428498</v>
+      </c>
+      <c r="J188">
+        <v>1</v>
+      </c>
+      <c r="K188">
+        <v>630</v>
+      </c>
+      <c r="L188">
+        <v>286</v>
+      </c>
+      <c r="M188">
+        <v>0.40559440559440502</v>
+      </c>
+      <c r="N188">
+        <v>32</v>
+      </c>
+      <c r="O188">
+        <v>13</v>
+      </c>
+      <c r="P188">
+        <v>65</v>
+      </c>
+      <c r="Q188">
+        <v>16</v>
+      </c>
+      <c r="R188">
+        <v>0</v>
+      </c>
+      <c r="S188">
+        <v>232</v>
+      </c>
+      <c r="T188">
+        <v>49</v>
+      </c>
+      <c r="U188">
+        <v>31</v>
+      </c>
+      <c r="V188">
+        <v>80</v>
+      </c>
+      <c r="W188">
+        <v>0.38750000000000001</v>
+      </c>
+      <c r="X188">
+        <v>101</v>
+      </c>
+      <c r="Y188">
+        <v>96</v>
+      </c>
+      <c r="Z188">
+        <v>57</v>
+      </c>
+      <c r="AA188">
+        <v>2503</v>
+      </c>
+      <c r="AB188">
+        <v>0.25598086124401898</v>
+      </c>
+      <c r="AC188">
+        <v>0.83405275779376498</v>
+      </c>
+      <c r="AD188">
+        <v>0.20047961630695399</v>
+      </c>
+      <c r="AE188">
+        <v>52</v>
+      </c>
+      <c r="AF188">
+        <v>140</v>
+      </c>
+      <c r="AG188">
+        <v>50</v>
+      </c>
+      <c r="AH188">
+        <v>8</v>
+      </c>
+      <c r="AI188">
+        <v>15</v>
+      </c>
+      <c r="AJ188">
+        <v>86</v>
+      </c>
+      <c r="AK188">
+        <v>0.27906976744186002</v>
+      </c>
+      <c r="AL188">
+        <v>0.27906976744186002</v>
+      </c>
+      <c r="AM188">
+        <v>176</v>
+      </c>
+      <c r="AN188">
+        <v>0.70454545454545403</v>
+      </c>
+      <c r="AO188" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP188">
+        <v>0.452442648310797</v>
+      </c>
+      <c r="AQ188">
+        <v>11.5714285714285</v>
+      </c>
+      <c r="AR188">
+        <v>2027</v>
+      </c>
+      <c r="AS188">
+        <v>0.625</v>
+      </c>
+      <c r="AT188">
+        <v>90</v>
+      </c>
+      <c r="AU188">
+        <v>0.260713712527394</v>
+      </c>
+      <c r="AV188">
+        <v>0.190514858901177</v>
+      </c>
+    </row>
+    <row r="189" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>20</v>
+      </c>
+      <c r="B189" t="s">
+        <v>61</v>
+      </c>
+      <c r="C189">
+        <v>7</v>
+      </c>
+      <c r="D189">
+        <v>0.14285714285714199</v>
+      </c>
+      <c r="E189">
+        <v>0.42857142857142799</v>
+      </c>
+      <c r="F189">
+        <v>0.42857142857142799</v>
+      </c>
+      <c r="G189">
+        <v>1.1428571428571399</v>
+      </c>
+      <c r="H189">
+        <v>1.28571428571428</v>
+      </c>
+      <c r="I189">
+        <v>-0.14285714285714199</v>
+      </c>
+      <c r="J189">
+        <v>0.85714285714285698</v>
+      </c>
+      <c r="K189">
+        <v>630</v>
+      </c>
+      <c r="L189">
+        <v>302</v>
+      </c>
+      <c r="M189">
+        <v>0.50331125827814505</v>
+      </c>
+      <c r="N189">
+        <v>31</v>
+      </c>
+      <c r="O189">
+        <v>14</v>
+      </c>
+      <c r="P189">
+        <v>58</v>
+      </c>
+      <c r="Q189">
+        <v>15</v>
+      </c>
+      <c r="R189">
+        <v>0</v>
+      </c>
+      <c r="S189">
+        <v>231</v>
+      </c>
+      <c r="T189">
+        <v>37</v>
+      </c>
+      <c r="U189">
+        <v>32</v>
+      </c>
+      <c r="V189">
+        <v>69</v>
+      </c>
+      <c r="W189">
+        <v>0.46376811594202899</v>
+      </c>
+      <c r="X189">
+        <v>78</v>
+      </c>
+      <c r="Y189">
+        <v>87</v>
+      </c>
+      <c r="Z189">
+        <v>49</v>
+      </c>
+      <c r="AA189">
+        <v>2577</v>
+      </c>
+      <c r="AB189">
+        <v>0.31610337972166902</v>
+      </c>
+      <c r="AC189">
+        <v>0.82931533269045299</v>
+      </c>
+      <c r="AD189">
+        <v>0.242526518804243</v>
+      </c>
+      <c r="AE189">
+        <v>72</v>
+      </c>
+      <c r="AF189">
+        <v>104</v>
+      </c>
+      <c r="AG189">
+        <v>50</v>
+      </c>
+      <c r="AH189">
+        <v>13</v>
+      </c>
+      <c r="AI189">
+        <v>16</v>
+      </c>
+      <c r="AJ189">
+        <v>96</v>
+      </c>
+      <c r="AK189">
+        <v>0.30208333333333298</v>
+      </c>
+      <c r="AL189">
+        <v>0.36458333333333298</v>
+      </c>
+      <c r="AM189">
+        <v>127</v>
+      </c>
+      <c r="AN189">
+        <v>0.70866141732283405</v>
+      </c>
+      <c r="AO189" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP189">
+        <v>0.50098719764041399</v>
+      </c>
+      <c r="AQ189">
+        <v>13.714285714285699</v>
+      </c>
+      <c r="AR189">
+        <v>2027</v>
+      </c>
+      <c r="AS189">
+        <v>0.64</v>
+      </c>
+      <c r="AT189">
+        <v>90</v>
+      </c>
+      <c r="AU189">
+        <v>0.25871871500159999</v>
+      </c>
+      <c r="AV189">
+        <v>0.24092414214125599</v>
+      </c>
+    </row>
+    <row r="190" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>21</v>
+      </c>
+      <c r="B190" t="s">
+        <v>87</v>
+      </c>
+      <c r="C190">
+        <v>7</v>
+      </c>
+      <c r="D190">
+        <v>0</v>
+      </c>
+      <c r="E190">
+        <v>0.85714285714285698</v>
+      </c>
+      <c r="F190">
+        <v>0.14285714285714199</v>
+      </c>
+      <c r="G190">
+        <v>1.1428571428571399</v>
+      </c>
+      <c r="H190">
+        <v>1.4285714285714199</v>
+      </c>
+      <c r="I190">
+        <v>-0.28571428571428498</v>
+      </c>
+      <c r="J190">
+        <v>0.85714285714285698</v>
+      </c>
+      <c r="K190">
+        <v>630</v>
+      </c>
+      <c r="L190">
+        <v>322</v>
+      </c>
+      <c r="M190">
+        <v>0.453416149068323</v>
+      </c>
+      <c r="N190">
+        <v>41</v>
+      </c>
+      <c r="O190">
+        <v>12</v>
+      </c>
+      <c r="P190">
+        <v>46</v>
+      </c>
+      <c r="Q190">
+        <v>12</v>
+      </c>
+      <c r="R190">
+        <v>0</v>
+      </c>
+      <c r="S190">
+        <v>224</v>
+      </c>
+      <c r="T190">
+        <v>54</v>
+      </c>
+      <c r="U190">
+        <v>34</v>
+      </c>
+      <c r="V190">
+        <v>88</v>
+      </c>
+      <c r="W190">
+        <v>0.38636363636363602</v>
+      </c>
+      <c r="X190">
+        <v>65</v>
+      </c>
+      <c r="Y190">
+        <v>87</v>
+      </c>
+      <c r="Z190">
+        <v>62</v>
+      </c>
+      <c r="AA190">
+        <v>2145</v>
+      </c>
+      <c r="AB190">
+        <v>0.39915966386554602</v>
+      </c>
+      <c r="AC190">
+        <v>0.81845416417016104</v>
+      </c>
+      <c r="AD190">
+        <v>0.28520071899340899</v>
+      </c>
+      <c r="AE190">
+        <v>69</v>
+      </c>
+      <c r="AF190">
+        <v>114</v>
+      </c>
+      <c r="AG190">
+        <v>48</v>
+      </c>
+      <c r="AH190">
+        <v>17</v>
+      </c>
+      <c r="AI190">
+        <v>25</v>
+      </c>
+      <c r="AJ190">
+        <v>100</v>
+      </c>
+      <c r="AK190">
+        <v>0.23</v>
+      </c>
+      <c r="AL190">
+        <v>0.3</v>
+      </c>
+      <c r="AM190">
+        <v>142</v>
+      </c>
+      <c r="AN190">
+        <v>0.68309859154929498</v>
+      </c>
+      <c r="AO190" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP190">
+        <v>0.43701553717830999</v>
+      </c>
+      <c r="AQ190">
+        <v>16.428571428571399</v>
+      </c>
+      <c r="AR190">
+        <v>2027</v>
+      </c>
+      <c r="AS190">
+        <v>0.71428571428571397</v>
+      </c>
+      <c r="AT190">
+        <v>90</v>
+      </c>
+      <c r="AU190">
+        <v>0.24639675199007099</v>
+      </c>
+      <c r="AV190">
+        <v>0.18944610515278601</v>
+      </c>
+    </row>
+    <row r="191" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>22</v>
+      </c>
+      <c r="B191" t="s">
+        <v>65</v>
+      </c>
+      <c r="C191">
+        <v>8</v>
+      </c>
+      <c r="D191">
+        <v>0.125</v>
+      </c>
+      <c r="E191">
+        <v>0.25</v>
+      </c>
+      <c r="F191">
+        <v>0.625</v>
+      </c>
+      <c r="G191">
+        <v>0.5</v>
+      </c>
+      <c r="H191">
+        <v>1.625</v>
+      </c>
+      <c r="I191">
+        <v>-1.125</v>
+      </c>
+      <c r="J191">
+        <v>0.625</v>
+      </c>
+      <c r="K191">
+        <v>720</v>
+      </c>
+      <c r="L191">
+        <v>305</v>
+      </c>
+      <c r="M191">
+        <v>0.44262295081967201</v>
+      </c>
+      <c r="N191">
+        <v>31</v>
+      </c>
+      <c r="O191">
+        <v>13</v>
+      </c>
+      <c r="P191">
+        <v>51</v>
+      </c>
+      <c r="Q191">
+        <v>12</v>
+      </c>
+      <c r="R191">
+        <v>1</v>
+      </c>
+      <c r="S191">
+        <v>241</v>
+      </c>
+      <c r="T191">
+        <v>65</v>
+      </c>
+      <c r="U191">
+        <v>48</v>
+      </c>
+      <c r="V191">
+        <v>113</v>
+      </c>
+      <c r="W191">
+        <v>0.42477876106194601</v>
+      </c>
+      <c r="X191">
+        <v>96</v>
+      </c>
+      <c r="Y191">
+        <v>75</v>
+      </c>
+      <c r="Z191">
+        <v>49</v>
+      </c>
+      <c r="AA191">
+        <v>3894</v>
+      </c>
+      <c r="AB191">
+        <v>0.32193158953722301</v>
+      </c>
+      <c r="AC191">
+        <v>0.87665587282896595</v>
+      </c>
+      <c r="AD191">
+        <v>0.14630556373270501</v>
+      </c>
+      <c r="AE191">
+        <v>82</v>
+      </c>
+      <c r="AF191">
+        <v>153</v>
+      </c>
+      <c r="AG191">
+        <v>81</v>
+      </c>
+      <c r="AH191">
+        <v>13</v>
+      </c>
+      <c r="AI191">
+        <v>25</v>
+      </c>
+      <c r="AJ191">
+        <v>107</v>
+      </c>
+      <c r="AK191">
+        <v>0.21495327102803699</v>
+      </c>
+      <c r="AL191">
+        <v>0.401869158878504</v>
+      </c>
+      <c r="AM191">
+        <v>153</v>
+      </c>
+      <c r="AN191">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="AO191" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP191">
+        <v>0.57391503380872699</v>
+      </c>
+      <c r="AQ191">
+        <v>12.875</v>
+      </c>
+      <c r="AR191">
+        <v>2027</v>
+      </c>
+      <c r="AS191">
+        <v>0.65789473684210498</v>
+      </c>
+      <c r="AT191">
+        <v>90</v>
+      </c>
+      <c r="AU191">
+        <v>0.28198880444729002</v>
+      </c>
+      <c r="AV191">
+        <v>0.290386195552709</v>
+      </c>
+    </row>
+    <row r="192" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>23</v>
+      </c>
+      <c r="B192" t="s">
+        <v>63</v>
+      </c>
+      <c r="C192">
+        <v>7</v>
+      </c>
+      <c r="D192">
+        <v>0.14285714285714199</v>
+      </c>
+      <c r="E192">
+        <v>0.14285714285714199</v>
+      </c>
+      <c r="F192">
+        <v>0.71428571428571397</v>
+      </c>
+      <c r="G192">
+        <v>0.71428571428571397</v>
+      </c>
+      <c r="H192">
+        <v>1.71428571428571</v>
+      </c>
+      <c r="I192">
+        <v>-1</v>
+      </c>
+      <c r="J192">
+        <v>0.57142857142857095</v>
+      </c>
+      <c r="K192">
+        <v>630</v>
+      </c>
+      <c r="L192">
+        <v>256</v>
+      </c>
+      <c r="M192">
+        <v>0.453125</v>
+      </c>
+      <c r="N192">
+        <v>29</v>
+      </c>
+      <c r="O192">
+        <v>10</v>
+      </c>
+      <c r="P192">
+        <v>41</v>
+      </c>
+      <c r="Q192">
+        <v>17</v>
+      </c>
+      <c r="R192">
+        <v>0</v>
+      </c>
+      <c r="S192">
+        <v>208</v>
+      </c>
+      <c r="T192">
+        <v>49</v>
+      </c>
+      <c r="U192">
+        <v>30</v>
+      </c>
+      <c r="V192">
+        <v>79</v>
+      </c>
+      <c r="W192">
+        <v>0.379746835443038</v>
+      </c>
+      <c r="X192">
+        <v>72</v>
+      </c>
+      <c r="Y192">
+        <v>76</v>
+      </c>
+      <c r="Z192">
+        <v>49</v>
+      </c>
+      <c r="AA192">
+        <v>3055</v>
+      </c>
+      <c r="AB192">
+        <v>0.37096774193548299</v>
+      </c>
+      <c r="AC192">
+        <v>0.86768542676108795</v>
+      </c>
+      <c r="AD192">
+        <v>0.13865076407006999</v>
+      </c>
+      <c r="AE192">
+        <v>73</v>
+      </c>
+      <c r="AF192">
+        <v>118</v>
+      </c>
+      <c r="AG192">
+        <v>44</v>
+      </c>
+      <c r="AH192">
+        <v>18</v>
+      </c>
+      <c r="AI192">
+        <v>14</v>
+      </c>
+      <c r="AJ192">
+        <v>100</v>
+      </c>
+      <c r="AK192">
+        <v>0.22</v>
+      </c>
+      <c r="AL192">
+        <v>0.27</v>
+      </c>
+      <c r="AM192">
+        <v>110</v>
+      </c>
+      <c r="AN192">
+        <v>0.75454545454545396</v>
+      </c>
+      <c r="AO192" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP192">
+        <v>0.53694081782847503</v>
+      </c>
+      <c r="AQ192">
+        <v>13.714285714285699</v>
+      </c>
+      <c r="AR192">
+        <v>2027</v>
+      </c>
+      <c r="AS192">
+        <v>0.53846153846153799</v>
+      </c>
+      <c r="AT192">
+        <v>90</v>
+      </c>
+      <c r="AU192">
+        <v>0.26587821746840901</v>
+      </c>
+      <c r="AV192">
+        <v>0.26962178253159003</v>
       </c>
     </row>
   </sheetData>
@@ -25227,7 +28740,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BDE5930-7F8E-4042-92CB-70509AE8AF60}">
-  <dimension ref="A1:AM168"/>
+  <dimension ref="A1:AM192"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:39" x14ac:dyDescent="0.25">
@@ -45217,6 +48730,2862 @@
       </c>
       <c r="AM168">
         <v>0.63934426229508201</v>
+      </c>
+    </row>
+    <row r="169" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>0</v>
+      </c>
+      <c r="B169" t="s">
+        <v>48</v>
+      </c>
+      <c r="C169" t="s">
+        <v>55</v>
+      </c>
+      <c r="D169">
+        <v>2027</v>
+      </c>
+      <c r="E169">
+        <v>9</v>
+      </c>
+      <c r="F169">
+        <v>0.55555555555555503</v>
+      </c>
+      <c r="G169">
+        <v>0.11111111111111099</v>
+      </c>
+      <c r="H169">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="I169">
+        <v>1.7777777777777699</v>
+      </c>
+      <c r="J169">
+        <v>1.2222222222222201</v>
+      </c>
+      <c r="K169">
+        <v>0.55555555555555503</v>
+      </c>
+      <c r="L169">
+        <v>1.7777777777777699</v>
+      </c>
+      <c r="M169">
+        <v>90</v>
+      </c>
+      <c r="N169">
+        <v>738.99154791062699</v>
+      </c>
+      <c r="O169">
+        <v>0.43136863835461597</v>
+      </c>
+      <c r="P169">
+        <v>0.320066334991708</v>
+      </c>
+      <c r="Q169">
+        <v>0.77581641659311495</v>
+      </c>
+      <c r="R169">
+        <v>0.26610767872903701</v>
+      </c>
+      <c r="S169">
+        <v>4.4963401882188898E-2</v>
+      </c>
+      <c r="T169">
+        <v>0.34883720930232498</v>
+      </c>
+      <c r="U169">
+        <v>0.27906976744186002</v>
+      </c>
+      <c r="V169">
+        <v>2.7187173231090898E-2</v>
+      </c>
+      <c r="W169">
+        <v>8.33042872080864E-2</v>
+      </c>
+      <c r="X169">
+        <v>3.2066922272568799E-2</v>
+      </c>
+      <c r="Y169">
+        <v>0.44565217391304301</v>
+      </c>
+      <c r="Z169">
+        <v>3.27640292784942E-2</v>
+      </c>
+      <c r="AA169">
+        <v>3.0672219248821998E-2</v>
+      </c>
+      <c r="AB169">
+        <v>5.6320540517233598E-2</v>
+      </c>
+      <c r="AC169">
+        <v>0.70892018779342703</v>
+      </c>
+      <c r="AD169">
+        <v>1.93023448721035E-2</v>
+      </c>
+      <c r="AE169">
+        <v>2.6970399684309001E-2</v>
+      </c>
+      <c r="AF169">
+        <v>8.8881143255489695E-2</v>
+      </c>
+      <c r="AG169">
+        <v>8.1968861785645195E-3</v>
+      </c>
+      <c r="AH169">
+        <v>0.11528523786626201</v>
+      </c>
+      <c r="AI169">
+        <v>0.46788990825687998</v>
+      </c>
+      <c r="AJ169">
+        <v>3.14360867780073E-3</v>
+      </c>
+      <c r="AK169">
+        <v>3.701819564513E-3</v>
+      </c>
+      <c r="AL169">
+        <v>0</v>
+      </c>
+      <c r="AM169">
+        <v>0.592592592592592</v>
+      </c>
+    </row>
+    <row r="170" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>1</v>
+      </c>
+      <c r="B170" t="s">
+        <v>48</v>
+      </c>
+      <c r="C170" t="s">
+        <v>51</v>
+      </c>
+      <c r="D170">
+        <v>2027</v>
+      </c>
+      <c r="E170">
+        <v>8</v>
+      </c>
+      <c r="F170">
+        <v>0.625</v>
+      </c>
+      <c r="G170">
+        <v>0.125</v>
+      </c>
+      <c r="H170">
+        <v>0.25</v>
+      </c>
+      <c r="I170">
+        <v>1</v>
+      </c>
+      <c r="J170">
+        <v>0.625</v>
+      </c>
+      <c r="K170">
+        <v>0.375</v>
+      </c>
+      <c r="L170">
+        <v>2</v>
+      </c>
+      <c r="M170">
+        <v>90</v>
+      </c>
+      <c r="N170">
+        <v>724.44988859614796</v>
+      </c>
+      <c r="O170">
+        <v>0.48778391102354302</v>
+      </c>
+      <c r="P170">
+        <v>0.33169934640522802</v>
+      </c>
+      <c r="Q170">
+        <v>0.76975169300225699</v>
+      </c>
+      <c r="R170">
+        <v>0.27629796839729098</v>
+      </c>
+      <c r="S170">
+        <v>3.0774672798019102E-2</v>
+      </c>
+      <c r="T170">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="U170">
+        <v>0.21839080459770099</v>
+      </c>
+      <c r="V170">
+        <v>2.4407499115670299E-2</v>
+      </c>
+      <c r="W170">
+        <v>7.3929961089494095E-2</v>
+      </c>
+      <c r="X170">
+        <v>2.7237354085603099E-2</v>
+      </c>
+      <c r="Y170">
+        <v>0.51948051948051899</v>
+      </c>
+      <c r="Z170">
+        <v>3.6434382737884602E-2</v>
+      </c>
+      <c r="AA170">
+        <v>4.2107403330666003E-2</v>
+      </c>
+      <c r="AB170">
+        <v>6.3666393835967006E-2</v>
+      </c>
+      <c r="AC170">
+        <v>0.72486772486772399</v>
+      </c>
+      <c r="AD170">
+        <v>2.3243286638527601E-2</v>
+      </c>
+      <c r="AE170">
+        <v>3.3012204211242097E-2</v>
+      </c>
+      <c r="AF170">
+        <v>9.0201627166607706E-2</v>
+      </c>
+      <c r="AG170">
+        <v>3.3685922664532801E-3</v>
+      </c>
+      <c r="AH170">
+        <v>0.14619690436407201</v>
+      </c>
+      <c r="AI170">
+        <v>0.55299539170506895</v>
+      </c>
+      <c r="AJ170">
+        <v>3.4528070731146099E-3</v>
+      </c>
+      <c r="AK170">
+        <v>6.40032530626123E-3</v>
+      </c>
+      <c r="AL170">
+        <v>0</v>
+      </c>
+      <c r="AM170">
+        <v>0.70588235294117596</v>
+      </c>
+    </row>
+    <row r="171" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>2</v>
+      </c>
+      <c r="B171" t="s">
+        <v>48</v>
+      </c>
+      <c r="C171" t="s">
+        <v>56</v>
+      </c>
+      <c r="D171">
+        <v>2027</v>
+      </c>
+      <c r="E171">
+        <v>8</v>
+      </c>
+      <c r="F171">
+        <v>0.5</v>
+      </c>
+      <c r="G171">
+        <v>0.375</v>
+      </c>
+      <c r="H171">
+        <v>0.125</v>
+      </c>
+      <c r="I171">
+        <v>1.75</v>
+      </c>
+      <c r="J171">
+        <v>0.875</v>
+      </c>
+      <c r="K171">
+        <v>0.875</v>
+      </c>
+      <c r="L171">
+        <v>1.875</v>
+      </c>
+      <c r="M171">
+        <v>90</v>
+      </c>
+      <c r="N171">
+        <v>770.27917432888501</v>
+      </c>
+      <c r="O171">
+        <v>0.50663449435720398</v>
+      </c>
+      <c r="P171">
+        <v>0.38936170212765903</v>
+      </c>
+      <c r="Q171">
+        <v>0.84049773755656099</v>
+      </c>
+      <c r="R171">
+        <v>0.177224736048265</v>
+      </c>
+      <c r="S171">
+        <v>4.09993593850096E-2</v>
+      </c>
+      <c r="T171">
+        <v>0.390625</v>
+      </c>
+      <c r="U171">
+        <v>0.2890625</v>
+      </c>
+      <c r="V171">
+        <v>3.0749519538757202E-2</v>
+      </c>
+      <c r="W171">
+        <v>6.18193465727098E-2</v>
+      </c>
+      <c r="X171">
+        <v>3.6194746957078798E-2</v>
+      </c>
+      <c r="Y171">
+        <v>0.37168141592920301</v>
+      </c>
+      <c r="Z171">
+        <v>2.7226137091607899E-2</v>
+      </c>
+      <c r="AA171">
+        <v>3.2234367326226802E-2</v>
+      </c>
+      <c r="AB171">
+        <v>4.8680473104914003E-2</v>
+      </c>
+      <c r="AC171">
+        <v>0.74324324324324298</v>
+      </c>
+      <c r="AD171">
+        <v>1.90774827032771E-2</v>
+      </c>
+      <c r="AE171">
+        <v>2.96029904016369E-2</v>
+      </c>
+      <c r="AF171">
+        <v>8.48814862267777E-2</v>
+      </c>
+      <c r="AG171">
+        <v>3.2892211557374301E-3</v>
+      </c>
+      <c r="AH171">
+        <v>0.11972765006884201</v>
+      </c>
+      <c r="AI171">
+        <v>0.52747252747252704</v>
+      </c>
+      <c r="AJ171">
+        <v>2.7547227179301002E-3</v>
+      </c>
+      <c r="AK171">
+        <v>3.2892211557374301E-3</v>
+      </c>
+      <c r="AL171">
+        <v>3.2892211557374301E-4</v>
+      </c>
+      <c r="AM171">
+        <v>0.63157894736842102</v>
+      </c>
+    </row>
+    <row r="172" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>3</v>
+      </c>
+      <c r="B172" t="s">
+        <v>48</v>
+      </c>
+      <c r="C172" t="s">
+        <v>86</v>
+      </c>
+      <c r="D172">
+        <v>2027</v>
+      </c>
+      <c r="E172">
+        <v>7</v>
+      </c>
+      <c r="F172">
+        <v>0.57142857142857095</v>
+      </c>
+      <c r="G172">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="H172">
+        <v>0.14285714285714199</v>
+      </c>
+      <c r="I172">
+        <v>1.8571428571428501</v>
+      </c>
+      <c r="J172">
+        <v>0.85714285714285698</v>
+      </c>
+      <c r="K172">
+        <v>1</v>
+      </c>
+      <c r="L172">
+        <v>2</v>
+      </c>
+      <c r="M172">
+        <v>90</v>
+      </c>
+      <c r="N172">
+        <v>792.46968246129995</v>
+      </c>
+      <c r="O172">
+        <v>0.54026402096936399</v>
+      </c>
+      <c r="P172">
+        <v>0.34708737864077599</v>
+      </c>
+      <c r="Q172">
+        <v>0.86305609284332596</v>
+      </c>
+      <c r="R172">
+        <v>0.15938104448742699</v>
+      </c>
+      <c r="S172">
+        <v>3.4701368034701301E-2</v>
+      </c>
+      <c r="T172">
+        <v>0.36538461538461497</v>
+      </c>
+      <c r="U172">
+        <v>0.25961538461538403</v>
+      </c>
+      <c r="V172">
+        <v>2.5358692025358599E-2</v>
+      </c>
+      <c r="W172">
+        <v>6.1394728061394697E-2</v>
+      </c>
+      <c r="X172">
+        <v>3.3033033033033003E-2</v>
+      </c>
+      <c r="Y172">
+        <v>0.39393939393939298</v>
+      </c>
+      <c r="Z172">
+        <v>2.43576910243576E-2</v>
+      </c>
+      <c r="AA172">
+        <v>3.5290135020678098E-2</v>
+      </c>
+      <c r="AB172">
+        <v>5.09746394743128E-2</v>
+      </c>
+      <c r="AC172">
+        <v>0.79230769230769205</v>
+      </c>
+      <c r="AD172">
+        <v>2.3918869291792901E-2</v>
+      </c>
+      <c r="AE172">
+        <v>3.3721684575314603E-2</v>
+      </c>
+      <c r="AF172">
+        <v>6.9069069069068997E-2</v>
+      </c>
+      <c r="AG172">
+        <v>6.2738017814538798E-3</v>
+      </c>
+      <c r="AH172">
+        <v>0.101557166337284</v>
+      </c>
+      <c r="AI172">
+        <v>0.54054054054054002</v>
+      </c>
+      <c r="AJ172">
+        <v>5.2094961221001001E-3</v>
+      </c>
+      <c r="AK172">
+        <v>5.48957655877214E-3</v>
+      </c>
+      <c r="AL172">
+        <v>0</v>
+      </c>
+      <c r="AM172">
+        <v>0.72727272727272696</v>
+      </c>
+    </row>
+    <row r="173" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>4</v>
+      </c>
+      <c r="B173" t="s">
+        <v>48</v>
+      </c>
+      <c r="C173" t="s">
+        <v>50</v>
+      </c>
+      <c r="D173">
+        <v>2027</v>
+      </c>
+      <c r="E173">
+        <v>8</v>
+      </c>
+      <c r="F173">
+        <v>0.5</v>
+      </c>
+      <c r="G173">
+        <v>0.125</v>
+      </c>
+      <c r="H173">
+        <v>0.375</v>
+      </c>
+      <c r="I173">
+        <v>2.125</v>
+      </c>
+      <c r="J173">
+        <v>1.25</v>
+      </c>
+      <c r="K173">
+        <v>0.875</v>
+      </c>
+      <c r="L173">
+        <v>1.625</v>
+      </c>
+      <c r="M173">
+        <v>90</v>
+      </c>
+      <c r="N173">
+        <v>975.85005815522504</v>
+      </c>
+      <c r="O173">
+        <v>0.58346566180091397</v>
+      </c>
+      <c r="P173">
+        <v>0.42771084337349302</v>
+      </c>
+      <c r="Q173">
+        <v>0.913975844219866</v>
+      </c>
+      <c r="R173">
+        <v>0.122750801084545</v>
+      </c>
+      <c r="S173">
+        <v>2.8759604829857299E-2</v>
+      </c>
+      <c r="T173">
+        <v>0.32061068702290002</v>
+      </c>
+      <c r="U173">
+        <v>0.244274809160305</v>
+      </c>
+      <c r="V173">
+        <v>2.2832052689352299E-2</v>
+      </c>
+      <c r="W173">
+        <v>4.8298572996706902E-2</v>
+      </c>
+      <c r="X173">
+        <v>2.3710208562019702E-2</v>
+      </c>
+      <c r="Y173">
+        <v>0.53703703703703698</v>
+      </c>
+      <c r="Z173">
+        <v>1.6684961580680498E-2</v>
+      </c>
+      <c r="AA173">
+        <v>2.1834058011526901E-2</v>
+      </c>
+      <c r="AB173">
+        <v>4.3668116023053899E-2</v>
+      </c>
+      <c r="AC173">
+        <v>0.76056338028169002</v>
+      </c>
+      <c r="AD173">
+        <v>1.72212288541621E-2</v>
+      </c>
+      <c r="AE173">
+        <v>2.3371667730648599E-2</v>
+      </c>
+      <c r="AF173">
+        <v>4.1492864983534501E-2</v>
+      </c>
+      <c r="AG173">
+        <v>5.2278730450134999E-3</v>
+      </c>
+      <c r="AH173">
+        <v>8.6413666214634893E-2</v>
+      </c>
+      <c r="AI173">
+        <v>0.59074733096085397</v>
+      </c>
+      <c r="AJ173">
+        <v>2.7676974944189098E-3</v>
+      </c>
+      <c r="AK173">
+        <v>2.4601755505945801E-3</v>
+      </c>
+      <c r="AL173">
+        <v>0</v>
+      </c>
+      <c r="AM173">
+        <v>0.64285714285714202</v>
+      </c>
+    </row>
+    <row r="174" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>5</v>
+      </c>
+      <c r="B174" t="s">
+        <v>48</v>
+      </c>
+      <c r="C174" t="s">
+        <v>77</v>
+      </c>
+      <c r="D174">
+        <v>2027</v>
+      </c>
+      <c r="E174">
+        <v>8</v>
+      </c>
+      <c r="F174">
+        <v>0.375</v>
+      </c>
+      <c r="G174">
+        <v>0.5</v>
+      </c>
+      <c r="H174">
+        <v>0.125</v>
+      </c>
+      <c r="I174">
+        <v>1.625</v>
+      </c>
+      <c r="J174">
+        <v>1.375</v>
+      </c>
+      <c r="K174">
+        <v>0.25</v>
+      </c>
+      <c r="L174">
+        <v>1.625</v>
+      </c>
+      <c r="M174">
+        <v>90</v>
+      </c>
+      <c r="N174">
+        <v>751.09317997269602</v>
+      </c>
+      <c r="O174">
+        <v>0.45883121986612502</v>
+      </c>
+      <c r="P174">
+        <v>0.31490787269681703</v>
+      </c>
+      <c r="Q174">
+        <v>0.79768518518518505</v>
+      </c>
+      <c r="R174">
+        <v>0.27638888888888802</v>
+      </c>
+      <c r="S174">
+        <v>3.4820457018498299E-2</v>
+      </c>
+      <c r="T174">
+        <v>0.34375</v>
+      </c>
+      <c r="U174">
+        <v>0.29166666666666602</v>
+      </c>
+      <c r="V174">
+        <v>2.1400072542618699E-2</v>
+      </c>
+      <c r="W174">
+        <v>9.2129125861443603E-2</v>
+      </c>
+      <c r="X174">
+        <v>2.97424737033006E-2</v>
+      </c>
+      <c r="Y174">
+        <v>0.39024390243902402</v>
+      </c>
+      <c r="Z174">
+        <v>3.1556039173014097E-2</v>
+      </c>
+      <c r="AA174">
+        <v>2.58322804031186E-2</v>
+      </c>
+      <c r="AB174">
+        <v>4.3668854967176797E-2</v>
+      </c>
+      <c r="AC174">
+        <v>0.75352112676056304</v>
+      </c>
+      <c r="AD174">
+        <v>2.0296791745307501E-2</v>
+      </c>
+      <c r="AE174">
+        <v>3.5365621980459998E-2</v>
+      </c>
+      <c r="AF174">
+        <v>0.10083424011606799</v>
+      </c>
+      <c r="AG174">
+        <v>2.4602171812493898E-3</v>
+      </c>
+      <c r="AH174">
+        <v>0.13684958070699699</v>
+      </c>
+      <c r="AI174">
+        <v>0.50337078651685396</v>
+      </c>
+      <c r="AJ174">
+        <v>3.8440893457021802E-3</v>
+      </c>
+      <c r="AK174">
+        <v>4.9204343624987901E-3</v>
+      </c>
+      <c r="AL174">
+        <v>0</v>
+      </c>
+      <c r="AM174">
+        <v>0.64516129032257996</v>
+      </c>
+    </row>
+    <row r="175" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>6</v>
+      </c>
+      <c r="B175" t="s">
+        <v>48</v>
+      </c>
+      <c r="C175" t="s">
+        <v>59</v>
+      </c>
+      <c r="D175">
+        <v>2027</v>
+      </c>
+      <c r="E175">
+        <v>8</v>
+      </c>
+      <c r="F175">
+        <v>0.375</v>
+      </c>
+      <c r="G175">
+        <v>0.375</v>
+      </c>
+      <c r="H175">
+        <v>0.25</v>
+      </c>
+      <c r="I175">
+        <v>2.125</v>
+      </c>
+      <c r="J175">
+        <v>1.25</v>
+      </c>
+      <c r="K175">
+        <v>0.875</v>
+      </c>
+      <c r="L175">
+        <v>1.5</v>
+      </c>
+      <c r="M175">
+        <v>90</v>
+      </c>
+      <c r="N175">
+        <v>759.04692513193402</v>
+      </c>
+      <c r="O175">
+        <v>0.49618144482244803</v>
+      </c>
+      <c r="P175">
+        <v>0.34313725490196001</v>
+      </c>
+      <c r="Q175">
+        <v>0.84218937275269601</v>
+      </c>
+      <c r="R175">
+        <v>0.20375549340790999</v>
+      </c>
+      <c r="S175">
+        <v>4.4805841354132098E-2</v>
+      </c>
+      <c r="T175">
+        <v>0.31111111111111101</v>
+      </c>
+      <c r="U175">
+        <v>0.41481481481481403</v>
+      </c>
+      <c r="V175">
+        <v>3.2857616993030199E-2</v>
+      </c>
+      <c r="W175">
+        <v>7.0029870560902693E-2</v>
+      </c>
+      <c r="X175">
+        <v>2.8874875539329499E-2</v>
+      </c>
+      <c r="Y175">
+        <v>0.41379310344827502</v>
+      </c>
+      <c r="Z175">
+        <v>3.2857616993030199E-2</v>
+      </c>
+      <c r="AA175">
+        <v>3.17058181112835E-2</v>
+      </c>
+      <c r="AB175">
+        <v>3.5628187362163902E-2</v>
+      </c>
+      <c r="AC175">
+        <v>0.73394495412843996</v>
+      </c>
+      <c r="AD175">
+        <v>1.9611846254402099E-2</v>
+      </c>
+      <c r="AE175">
+        <v>2.58222642349628E-2</v>
+      </c>
+      <c r="AF175">
+        <v>8.9943577829405902E-2</v>
+      </c>
+      <c r="AG175">
+        <v>7.8447385017608694E-3</v>
+      </c>
+      <c r="AH175">
+        <v>0.124535223715453</v>
+      </c>
+      <c r="AI175">
+        <v>0.54068241469816203</v>
+      </c>
+      <c r="AJ175">
+        <v>3.5955051466404001E-3</v>
+      </c>
+      <c r="AK175">
+        <v>4.2492333551204702E-3</v>
+      </c>
+      <c r="AL175">
+        <v>0</v>
+      </c>
+      <c r="AM175">
+        <v>0.61538461538461497</v>
+      </c>
+    </row>
+    <row r="176" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>7</v>
+      </c>
+      <c r="B176" t="s">
+        <v>48</v>
+      </c>
+      <c r="C176" t="s">
+        <v>64</v>
+      </c>
+      <c r="D176">
+        <v>2027</v>
+      </c>
+      <c r="E176">
+        <v>9</v>
+      </c>
+      <c r="F176">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G176">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="H176">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="I176">
+        <v>1.55555555555555</v>
+      </c>
+      <c r="J176">
+        <v>1.6666666666666601</v>
+      </c>
+      <c r="K176">
+        <v>-0.11111111111111099</v>
+      </c>
+      <c r="L176">
+        <v>1.3333333333333299</v>
+      </c>
+      <c r="M176">
+        <v>90</v>
+      </c>
+      <c r="N176">
+        <v>784.17892972694801</v>
+      </c>
+      <c r="O176">
+        <v>0.455678314970484</v>
+      </c>
+      <c r="P176">
+        <v>0.29144851657940601</v>
+      </c>
+      <c r="Q176">
+        <v>0.83049564888384397</v>
+      </c>
+      <c r="R176">
+        <v>0.21679909194097599</v>
+      </c>
+      <c r="S176">
+        <v>2.5497512437810899E-2</v>
+      </c>
+      <c r="T176">
+        <v>0.353658536585365</v>
+      </c>
+      <c r="U176">
+        <v>0.25609756097560898</v>
+      </c>
+      <c r="V176">
+        <v>1.7101990049751201E-2</v>
+      </c>
+      <c r="W176">
+        <v>8.2089552238805902E-2</v>
+      </c>
+      <c r="X176">
+        <v>3.60696517412935E-2</v>
+      </c>
+      <c r="Y176">
+        <v>0.45689655172413701</v>
+      </c>
+      <c r="Z176">
+        <v>3.7624378109452697E-2</v>
+      </c>
+      <c r="AA176">
+        <v>2.9675055274521599E-2</v>
+      </c>
+      <c r="AB176">
+        <v>5.5445498012921902E-2</v>
+      </c>
+      <c r="AC176">
+        <v>0.79812206572769895</v>
+      </c>
+      <c r="AD176">
+        <v>2.0824600192646699E-2</v>
+      </c>
+      <c r="AE176">
+        <v>3.2017822796194299E-2</v>
+      </c>
+      <c r="AF176">
+        <v>9.1106965174129306E-2</v>
+      </c>
+      <c r="AG176">
+        <v>3.1236900288970099E-3</v>
+      </c>
+      <c r="AH176">
+        <v>8.7983935813932504E-2</v>
+      </c>
+      <c r="AI176">
+        <v>0.523668639053254</v>
+      </c>
+      <c r="AJ176">
+        <v>3.3550744754819702E-3</v>
+      </c>
+      <c r="AK176">
+        <v>3.9046125361212598E-3</v>
+      </c>
+      <c r="AL176">
+        <v>2.6030750240808398E-4</v>
+      </c>
+      <c r="AM176">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="177" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>8</v>
+      </c>
+      <c r="B177" t="s">
+        <v>48</v>
+      </c>
+      <c r="C177" t="s">
+        <v>66</v>
+      </c>
+      <c r="D177">
+        <v>2027</v>
+      </c>
+      <c r="E177">
+        <v>8</v>
+      </c>
+      <c r="F177">
+        <v>0.375</v>
+      </c>
+      <c r="G177">
+        <v>0.375</v>
+      </c>
+      <c r="H177">
+        <v>0.25</v>
+      </c>
+      <c r="I177">
+        <v>0.75</v>
+      </c>
+      <c r="J177">
+        <v>1</v>
+      </c>
+      <c r="K177">
+        <v>-0.25</v>
+      </c>
+      <c r="L177">
+        <v>1.5</v>
+      </c>
+      <c r="M177">
+        <v>90</v>
+      </c>
+      <c r="N177">
+        <v>717.16531569190397</v>
+      </c>
+      <c r="O177">
+        <v>0.45421884309299598</v>
+      </c>
+      <c r="P177">
+        <v>0.31851851851851798</v>
+      </c>
+      <c r="Q177">
+        <v>0.80687318489835402</v>
+      </c>
+      <c r="R177">
+        <v>0.26137463697967001</v>
+      </c>
+      <c r="S177">
+        <v>3.2617037605525701E-2</v>
+      </c>
+      <c r="T177">
+        <v>0.247058823529411</v>
+      </c>
+      <c r="U177">
+        <v>0.28235294117646997</v>
+      </c>
+      <c r="V177">
+        <v>2.5709900230237899E-2</v>
+      </c>
+      <c r="W177">
+        <v>8.2885648503453493E-2</v>
+      </c>
+      <c r="X177">
+        <v>2.3407521105141899E-2</v>
+      </c>
+      <c r="Y177">
+        <v>0.40983606557377</v>
+      </c>
+      <c r="Z177">
+        <v>3.2233307751342997E-2</v>
+      </c>
+      <c r="AA177">
+        <v>3.1616034181301003E-2</v>
+      </c>
+      <c r="AB177">
+        <v>5.1735328660310803E-2</v>
+      </c>
+      <c r="AC177">
+        <v>0.77160493827160404</v>
+      </c>
+      <c r="AD177">
+        <v>1.9799940598390499E-2</v>
+      </c>
+      <c r="AE177">
+        <v>3.38515113456355E-2</v>
+      </c>
+      <c r="AF177">
+        <v>0.10552570990023</v>
+      </c>
+      <c r="AG177">
+        <v>5.4290159705264497E-3</v>
+      </c>
+      <c r="AH177">
+        <v>0.134767337621303</v>
+      </c>
+      <c r="AI177">
+        <v>0.523696682464455</v>
+      </c>
+      <c r="AJ177">
+        <v>4.3112773883592402E-3</v>
+      </c>
+      <c r="AK177">
+        <v>5.1096620899072397E-3</v>
+      </c>
+      <c r="AL177">
+        <v>0</v>
+      </c>
+      <c r="AM177">
+        <v>0.77142857142857102</v>
+      </c>
+    </row>
+    <row r="178" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>9</v>
+      </c>
+      <c r="B178" t="s">
+        <v>48</v>
+      </c>
+      <c r="C178" t="s">
+        <v>81</v>
+      </c>
+      <c r="D178">
+        <v>2027</v>
+      </c>
+      <c r="E178">
+        <v>6</v>
+      </c>
+      <c r="F178">
+        <v>0.5</v>
+      </c>
+      <c r="G178">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="H178">
+        <v>0.16666666666666599</v>
+      </c>
+      <c r="I178">
+        <v>2.1666666666666599</v>
+      </c>
+      <c r="J178">
+        <v>1.1666666666666601</v>
+      </c>
+      <c r="K178">
+        <v>1</v>
+      </c>
+      <c r="L178">
+        <v>1.8333333333333299</v>
+      </c>
+      <c r="M178">
+        <v>90</v>
+      </c>
+      <c r="N178">
+        <v>735.90988295384705</v>
+      </c>
+      <c r="O178">
+        <v>0.57751636422397901</v>
+      </c>
+      <c r="P178">
+        <v>0.36021505376343999</v>
+      </c>
+      <c r="Q178">
+        <v>0.86593204775022903</v>
+      </c>
+      <c r="R178">
+        <v>0.17079889807162499</v>
+      </c>
+      <c r="S178">
+        <v>2.62745098039215E-2</v>
+      </c>
+      <c r="T178">
+        <v>0.402985074626865</v>
+      </c>
+      <c r="U178">
+        <v>0.35820895522388002</v>
+      </c>
+      <c r="V178">
+        <v>2.1176470588235199E-2</v>
+      </c>
+      <c r="W178">
+        <v>7.0588235294117604E-2</v>
+      </c>
+      <c r="X178">
+        <v>4.2352941176470503E-2</v>
+      </c>
+      <c r="Y178">
+        <v>0.46296296296296202</v>
+      </c>
+      <c r="Z178">
+        <v>3.37254901960784E-2</v>
+      </c>
+      <c r="AA178">
+        <v>4.8781552141647602E-2</v>
+      </c>
+      <c r="AB178">
+        <v>7.61206637814721E-2</v>
+      </c>
+      <c r="AC178">
+        <v>0.79577464788732399</v>
+      </c>
+      <c r="AD178">
+        <v>2.89472946774612E-2</v>
+      </c>
+      <c r="AE178">
+        <v>4.3420942016191802E-2</v>
+      </c>
+      <c r="AF178">
+        <v>8.5882352941176396E-2</v>
+      </c>
+      <c r="AG178">
+        <v>3.2163660752734702E-3</v>
+      </c>
+      <c r="AH178">
+        <v>0.115253117697299</v>
+      </c>
+      <c r="AI178">
+        <v>0.46976744186046498</v>
+      </c>
+      <c r="AJ178">
+        <v>9.1130372132748293E-3</v>
+      </c>
+      <c r="AK178">
+        <v>5.8966711380013604E-3</v>
+      </c>
+      <c r="AL178">
+        <v>0</v>
+      </c>
+      <c r="AM178">
+        <v>0.69565217391304301</v>
+      </c>
+    </row>
+    <row r="179" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>10</v>
+      </c>
+      <c r="B179" t="s">
+        <v>48</v>
+      </c>
+      <c r="C179" t="s">
+        <v>67</v>
+      </c>
+      <c r="D179">
+        <v>2027</v>
+      </c>
+      <c r="E179">
+        <v>8</v>
+      </c>
+      <c r="F179">
+        <v>0.375</v>
+      </c>
+      <c r="G179">
+        <v>0.125</v>
+      </c>
+      <c r="H179">
+        <v>0.5</v>
+      </c>
+      <c r="I179">
+        <v>1.625</v>
+      </c>
+      <c r="J179">
+        <v>1.375</v>
+      </c>
+      <c r="K179">
+        <v>0.25</v>
+      </c>
+      <c r="L179">
+        <v>1.25</v>
+      </c>
+      <c r="M179">
+        <v>90</v>
+      </c>
+      <c r="N179">
+        <v>727.704733978371</v>
+      </c>
+      <c r="O179">
+        <v>0.50535606383856502</v>
+      </c>
+      <c r="P179">
+        <v>0.235067437379576</v>
+      </c>
+      <c r="Q179">
+        <v>0.80891456871646705</v>
+      </c>
+      <c r="R179">
+        <v>0.21419727610400299</v>
+      </c>
+      <c r="S179">
+        <v>2.8212100611828599E-2</v>
+      </c>
+      <c r="T179">
+        <v>0.38554216867469798</v>
+      </c>
+      <c r="U179">
+        <v>0.19277108433734899</v>
+      </c>
+      <c r="V179">
+        <v>2.0394289598912301E-2</v>
+      </c>
+      <c r="W179">
+        <v>7.9197824609109402E-2</v>
+      </c>
+      <c r="X179">
+        <v>3.7729435757987699E-2</v>
+      </c>
+      <c r="Y179">
+        <v>0.40540540540540498</v>
+      </c>
+      <c r="Z179">
+        <v>3.6369816451393602E-2</v>
+      </c>
+      <c r="AA179">
+        <v>3.4379322819917603E-2</v>
+      </c>
+      <c r="AB179">
+        <v>6.42441891079268E-2</v>
+      </c>
+      <c r="AC179">
+        <v>0.72432432432432403</v>
+      </c>
+      <c r="AD179">
+        <v>2.0488687337122599E-2</v>
+      </c>
+      <c r="AE179">
+        <v>4.4797299432013798E-2</v>
+      </c>
+      <c r="AF179">
+        <v>9.65329707681849E-2</v>
+      </c>
+      <c r="AG179">
+        <v>3.12539298362887E-3</v>
+      </c>
+      <c r="AH179">
+        <v>0.15140792676246501</v>
+      </c>
+      <c r="AI179">
+        <v>0.46788990825687998</v>
+      </c>
+      <c r="AJ179">
+        <v>5.5128459572342603E-3</v>
+      </c>
+      <c r="AK179">
+        <v>6.2507859672577401E-3</v>
+      </c>
+      <c r="AL179">
+        <v>0</v>
+      </c>
+      <c r="AM179">
+        <v>0.72499999999999998</v>
+      </c>
+    </row>
+    <row r="180" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>11</v>
+      </c>
+      <c r="B180" t="s">
+        <v>48</v>
+      </c>
+      <c r="C180" t="s">
+        <v>58</v>
+      </c>
+      <c r="D180">
+        <v>2027</v>
+      </c>
+      <c r="E180">
+        <v>8</v>
+      </c>
+      <c r="F180">
+        <v>0.25</v>
+      </c>
+      <c r="G180">
+        <v>0.5</v>
+      </c>
+      <c r="H180">
+        <v>0.25</v>
+      </c>
+      <c r="I180">
+        <v>1.625</v>
+      </c>
+      <c r="J180">
+        <v>2</v>
+      </c>
+      <c r="K180">
+        <v>-0.375</v>
+      </c>
+      <c r="L180">
+        <v>1.25</v>
+      </c>
+      <c r="M180">
+        <v>90</v>
+      </c>
+      <c r="N180">
+        <v>778.00513390896401</v>
+      </c>
+      <c r="O180">
+        <v>0.49148133262156801</v>
+      </c>
+      <c r="P180">
+        <v>0.394495412844036</v>
+      </c>
+      <c r="Q180">
+        <v>0.83651551312649097</v>
+      </c>
+      <c r="R180">
+        <v>0.21678599840891</v>
+      </c>
+      <c r="S180">
+        <v>3.3017325923504398E-2</v>
+      </c>
+      <c r="T180">
+        <v>0.396039603960396</v>
+      </c>
+      <c r="U180">
+        <v>0.287128712871287</v>
+      </c>
+      <c r="V180">
+        <v>2.6152337365152E-2</v>
+      </c>
+      <c r="W180">
+        <v>6.7996077149395207E-2</v>
+      </c>
+      <c r="X180">
+        <v>2.6806145799280801E-2</v>
+      </c>
+      <c r="Y180">
+        <v>0.41463414634146301</v>
+      </c>
+      <c r="Z180">
+        <v>3.2690421706440001E-2</v>
+      </c>
+      <c r="AA180">
+        <v>2.5276133294490199E-2</v>
+      </c>
+      <c r="AB180">
+        <v>4.1705619935908801E-2</v>
+      </c>
+      <c r="AC180">
+        <v>0.71212121212121204</v>
+      </c>
+      <c r="AD180">
+        <v>2.2116616632678901E-2</v>
+      </c>
+      <c r="AE180">
+        <v>2.4012326629765698E-2</v>
+      </c>
+      <c r="AF180">
+        <v>0.100686498855835</v>
+      </c>
+      <c r="AG180">
+        <v>5.3711783250791701E-3</v>
+      </c>
+      <c r="AH180">
+        <v>0.11848187481792199</v>
+      </c>
+      <c r="AI180">
+        <v>0.54400000000000004</v>
+      </c>
+      <c r="AJ180">
+        <v>4.8182629092621901E-3</v>
+      </c>
+      <c r="AK180">
+        <v>3.4754683279924E-3</v>
+      </c>
+      <c r="AL180">
+        <v>0</v>
+      </c>
+      <c r="AM180">
+        <v>0.61904761904761896</v>
+      </c>
+    </row>
+    <row r="181" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>12</v>
+      </c>
+      <c r="B181" t="s">
+        <v>48</v>
+      </c>
+      <c r="C181" t="s">
+        <v>53</v>
+      </c>
+      <c r="D181">
+        <v>2027</v>
+      </c>
+      <c r="E181">
+        <v>7</v>
+      </c>
+      <c r="F181">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="G181">
+        <v>0.42857142857142799</v>
+      </c>
+      <c r="H181">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="I181">
+        <v>1.5714285714285701</v>
+      </c>
+      <c r="J181">
+        <v>1.1428571428571399</v>
+      </c>
+      <c r="K181">
+        <v>0.42857142857142799</v>
+      </c>
+      <c r="L181">
+        <v>1.28571428571428</v>
+      </c>
+      <c r="M181">
+        <v>90</v>
+      </c>
+      <c r="N181">
+        <v>747.94631258235802</v>
+      </c>
+      <c r="O181">
+        <v>0.43395016876386999</v>
+      </c>
+      <c r="P181">
+        <v>0.35427574171029602</v>
+      </c>
+      <c r="Q181">
+        <v>0.77221895232489701</v>
+      </c>
+      <c r="R181">
+        <v>0.33725721012360199</v>
+      </c>
+      <c r="S181">
+        <v>3.2570422535211203E-2</v>
+      </c>
+      <c r="T181">
+        <v>0.36486486486486402</v>
+      </c>
+      <c r="U181">
+        <v>0.24324324324324301</v>
+      </c>
+      <c r="V181">
+        <v>2.5528169014084501E-2</v>
+      </c>
+      <c r="W181">
+        <v>8.3186619718309804E-2</v>
+      </c>
+      <c r="X181">
+        <v>3.1690140845070401E-2</v>
+      </c>
+      <c r="Y181">
+        <v>0.51388888888888795</v>
+      </c>
+      <c r="Z181">
+        <v>4.22535211267605E-2</v>
+      </c>
+      <c r="AA181">
+        <v>3.2730195815737398E-2</v>
+      </c>
+      <c r="AB181">
+        <v>5.9724171746242498E-2</v>
+      </c>
+      <c r="AC181">
+        <v>0.80790960451977401</v>
+      </c>
+      <c r="AD181">
+        <v>2.0920331346141401E-2</v>
+      </c>
+      <c r="AE181">
+        <v>3.5092168709656597E-2</v>
+      </c>
+      <c r="AF181">
+        <v>0.102992957746478</v>
+      </c>
+      <c r="AG181">
+        <v>4.7239457878383902E-3</v>
+      </c>
+      <c r="AH181">
+        <v>0.11269984950985799</v>
+      </c>
+      <c r="AI181">
+        <v>0.56886227544910095</v>
+      </c>
+      <c r="AJ181">
+        <v>3.71167169044445E-3</v>
+      </c>
+      <c r="AK181">
+        <v>4.7239457878383902E-3</v>
+      </c>
+      <c r="AL181">
+        <v>0</v>
+      </c>
+      <c r="AM181">
+        <v>0.52941176470588203</v>
+      </c>
+    </row>
+    <row r="182" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>13</v>
+      </c>
+      <c r="B182" t="s">
+        <v>48</v>
+      </c>
+      <c r="C182" t="s">
+        <v>116</v>
+      </c>
+      <c r="D182">
+        <v>2027</v>
+      </c>
+      <c r="E182">
+        <v>7</v>
+      </c>
+      <c r="F182">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="G182">
+        <v>0.42857142857142799</v>
+      </c>
+      <c r="H182">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="I182">
+        <v>1.28571428571428</v>
+      </c>
+      <c r="J182">
+        <v>1.5714285714285701</v>
+      </c>
+      <c r="K182">
+        <v>-0.28571428571428498</v>
+      </c>
+      <c r="L182">
+        <v>1.28571428571428</v>
+      </c>
+      <c r="M182">
+        <v>90</v>
+      </c>
+      <c r="N182">
+        <v>905.82491731507196</v>
+      </c>
+      <c r="O182">
+        <v>0.67562725235469401</v>
+      </c>
+      <c r="P182">
+        <v>0.352727272727272</v>
+      </c>
+      <c r="Q182">
+        <v>0.90646046395609803</v>
+      </c>
+      <c r="R182">
+        <v>6.8595659765527506E-2</v>
+      </c>
+      <c r="S182">
+        <v>2.4976657329598501E-2</v>
+      </c>
+      <c r="T182">
+        <v>0.32710280373831702</v>
+      </c>
+      <c r="U182">
+        <v>0.27102803738317699</v>
+      </c>
+      <c r="V182">
+        <v>1.8440709617180199E-2</v>
+      </c>
+      <c r="W182">
+        <v>4.7619047619047603E-2</v>
+      </c>
+      <c r="X182">
+        <v>2.7310924369747899E-2</v>
+      </c>
+      <c r="Y182">
+        <v>0.53846153846153799</v>
+      </c>
+      <c r="Z182">
+        <v>2.35760971055088E-2</v>
+      </c>
+      <c r="AA182">
+        <v>3.3061476892611401E-2</v>
+      </c>
+      <c r="AB182">
+        <v>6.2233368268445E-2</v>
+      </c>
+      <c r="AC182">
+        <v>0.7109375</v>
+      </c>
+      <c r="AD182">
+        <v>1.7989333015097302E-2</v>
+      </c>
+      <c r="AE182">
+        <v>3.9868251546972502E-2</v>
+      </c>
+      <c r="AF182">
+        <v>3.7815126050420103E-2</v>
+      </c>
+      <c r="AG182">
+        <v>3.8895855167778099E-3</v>
+      </c>
+      <c r="AH182">
+        <v>7.9736503093945102E-2</v>
+      </c>
+      <c r="AI182">
+        <v>0.48170731707316999</v>
+      </c>
+      <c r="AJ182">
+        <v>6.3900333489921197E-3</v>
+      </c>
+      <c r="AK182">
+        <v>6.8067746543611701E-3</v>
+      </c>
+      <c r="AL182">
+        <v>4.8619818959722602E-4</v>
+      </c>
+      <c r="AM182">
+        <v>0.62068965517241304</v>
+      </c>
+    </row>
+    <row r="183" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>14</v>
+      </c>
+      <c r="B183" t="s">
+        <v>48</v>
+      </c>
+      <c r="C183" t="s">
+        <v>60</v>
+      </c>
+      <c r="D183">
+        <v>2027</v>
+      </c>
+      <c r="E183">
+        <v>7</v>
+      </c>
+      <c r="F183">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="G183">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="H183">
+        <v>0.42857142857142799</v>
+      </c>
+      <c r="I183">
+        <v>1.8571428571428501</v>
+      </c>
+      <c r="J183">
+        <v>1.8571428571428501</v>
+      </c>
+      <c r="K183">
+        <v>0</v>
+      </c>
+      <c r="L183">
+        <v>1.1428571428571399</v>
+      </c>
+      <c r="M183">
+        <v>90</v>
+      </c>
+      <c r="N183">
+        <v>781.82108788931498</v>
+      </c>
+      <c r="O183">
+        <v>0.483669298513973</v>
+      </c>
+      <c r="P183">
+        <v>0.2890625</v>
+      </c>
+      <c r="Q183">
+        <v>0.83747072599531602</v>
+      </c>
+      <c r="R183">
+        <v>0.239812646370023</v>
+      </c>
+      <c r="S183">
+        <v>3.7778617302606697E-2</v>
+      </c>
+      <c r="T183">
+        <v>0.34</v>
+      </c>
+      <c r="U183">
+        <v>0.23</v>
+      </c>
+      <c r="V183">
+        <v>2.6445032111824699E-2</v>
+      </c>
+      <c r="W183">
+        <v>7.29127313940309E-2</v>
+      </c>
+      <c r="X183">
+        <v>3.21118247072157E-2</v>
+      </c>
+      <c r="Y183">
+        <v>0.45882352941176402</v>
+      </c>
+      <c r="Z183">
+        <v>2.7578390630902901E-2</v>
+      </c>
+      <c r="AA183">
+        <v>2.68955371635137E-2</v>
+      </c>
+      <c r="AB183">
+        <v>6.1576624558570901E-2</v>
+      </c>
+      <c r="AC183">
+        <v>0.72988505747126398</v>
+      </c>
+      <c r="AD183">
+        <v>1.7694432344416901E-2</v>
+      </c>
+      <c r="AE183">
+        <v>4.2112748979712303E-2</v>
+      </c>
+      <c r="AF183">
+        <v>8.8401964488099699E-2</v>
+      </c>
+      <c r="AG183">
+        <v>5.66221835021342E-3</v>
+      </c>
+      <c r="AH183">
+        <v>0.111474923769826</v>
+      </c>
+      <c r="AI183">
+        <v>0.49523809523809498</v>
+      </c>
+      <c r="AJ183">
+        <v>6.7238842908784301E-3</v>
+      </c>
+      <c r="AK183">
+        <v>3.8927751157717201E-3</v>
+      </c>
+      <c r="AL183">
+        <v>0</v>
+      </c>
+      <c r="AM183">
+        <v>0.71739130434782605</v>
+      </c>
+    </row>
+    <row r="184" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>48</v>
+      </c>
+      <c r="C184" t="s">
+        <v>54</v>
+      </c>
+      <c r="D184">
+        <v>2027</v>
+      </c>
+      <c r="E184">
+        <v>7</v>
+      </c>
+      <c r="F184">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="G184">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="H184">
+        <v>0.42857142857142799</v>
+      </c>
+      <c r="I184">
+        <v>1.71428571428571</v>
+      </c>
+      <c r="J184">
+        <v>2</v>
+      </c>
+      <c r="K184">
+        <v>-0.28571428571428498</v>
+      </c>
+      <c r="L184">
+        <v>1.1428571428571399</v>
+      </c>
+      <c r="M184">
+        <v>90</v>
+      </c>
+      <c r="N184">
+        <v>829.98734817221703</v>
+      </c>
+      <c r="O184">
+        <v>0.56851124766691596</v>
+      </c>
+      <c r="P184">
+        <v>0.32383419689119097</v>
+      </c>
+      <c r="Q184">
+        <v>0.88207062050051399</v>
+      </c>
+      <c r="R184">
+        <v>0.13232773397326</v>
+      </c>
+      <c r="S184">
+        <v>2.8458976687859499E-2</v>
+      </c>
+      <c r="T184">
+        <v>0.329787234042553</v>
+      </c>
+      <c r="U184">
+        <v>0.340425531914893</v>
+      </c>
+      <c r="V184">
+        <v>1.9981834695731102E-2</v>
+      </c>
+      <c r="W184">
+        <v>5.0257341810475302E-2</v>
+      </c>
+      <c r="X184">
+        <v>3.6633363608840397E-2</v>
+      </c>
+      <c r="Y184">
+        <v>0.38842975206611502</v>
+      </c>
+      <c r="Z184">
+        <v>2.8156221616712E-2</v>
+      </c>
+      <c r="AA184">
+        <v>3.2709571939009599E-2</v>
+      </c>
+      <c r="AB184">
+        <v>4.8665460689745997E-2</v>
+      </c>
+      <c r="AC184">
+        <v>0.76229508196721296</v>
+      </c>
+      <c r="AD184">
+        <v>2.2338244251030901E-2</v>
+      </c>
+      <c r="AE184">
+        <v>3.5900749689156797E-2</v>
+      </c>
+      <c r="AF184">
+        <v>7.6597033000302697E-2</v>
+      </c>
+      <c r="AG184">
+        <v>3.5900749689156798E-3</v>
+      </c>
+      <c r="AH184">
+        <v>0.103314379661018</v>
+      </c>
+      <c r="AI184">
+        <v>0.45559845559845502</v>
+      </c>
+      <c r="AJ184">
+        <v>4.2738987725186696E-3</v>
+      </c>
+      <c r="AK184">
+        <v>5.9834582815261397E-3</v>
+      </c>
+      <c r="AL184">
+        <v>3.9889721876840899E-4</v>
+      </c>
+      <c r="AM184">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="185" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>16</v>
+      </c>
+      <c r="B185" t="s">
+        <v>48</v>
+      </c>
+      <c r="C185" t="s">
+        <v>57</v>
+      </c>
+      <c r="D185">
+        <v>2027</v>
+      </c>
+      <c r="E185">
+        <v>7</v>
+      </c>
+      <c r="F185">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="G185">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="H185">
+        <v>0.42857142857142799</v>
+      </c>
+      <c r="I185">
+        <v>1.4285714285714199</v>
+      </c>
+      <c r="J185">
+        <v>1.8571428571428501</v>
+      </c>
+      <c r="K185">
+        <v>-0.42857142857142799</v>
+      </c>
+      <c r="L185">
+        <v>1.1428571428571399</v>
+      </c>
+      <c r="M185">
+        <v>90</v>
+      </c>
+      <c r="N185">
+        <v>782.65939827430202</v>
+      </c>
+      <c r="O185">
+        <v>0.46033525577040701</v>
+      </c>
+      <c r="P185">
+        <v>0.37837837837837801</v>
+      </c>
+      <c r="Q185">
+        <v>0.821166095051445</v>
+      </c>
+      <c r="R185">
+        <v>0.23566878980891701</v>
+      </c>
+      <c r="S185">
+        <v>3.2910388580491598E-2</v>
+      </c>
+      <c r="T185">
+        <v>0.32530120481927699</v>
+      </c>
+      <c r="U185">
+        <v>0.25301204819277101</v>
+      </c>
+      <c r="V185">
+        <v>2.3790642347343301E-2</v>
+      </c>
+      <c r="W185">
+        <v>7.7716098334654996E-2</v>
+      </c>
+      <c r="X185">
+        <v>3.5289452815225997E-2</v>
+      </c>
+      <c r="Y185">
+        <v>0.47191011235954999</v>
+      </c>
+      <c r="Z185">
+        <v>3.2513877874702599E-2</v>
+      </c>
+      <c r="AA185">
+        <v>3.3484228963562103E-2</v>
+      </c>
+      <c r="AB185">
+        <v>5.4792374667647102E-2</v>
+      </c>
+      <c r="AC185">
+        <v>0.70370370370370305</v>
+      </c>
+      <c r="AD185">
+        <v>2.4690391053939699E-2</v>
+      </c>
+      <c r="AE185">
+        <v>2.8749085473765399E-2</v>
+      </c>
+      <c r="AF185">
+        <v>9.2783505154639095E-2</v>
+      </c>
+      <c r="AG185">
+        <v>4.3969189548111898E-3</v>
+      </c>
+      <c r="AH185">
+        <v>9.1320624446078594E-2</v>
+      </c>
+      <c r="AI185">
+        <v>0.54444444444444395</v>
+      </c>
+      <c r="AJ185">
+        <v>4.5901901176600302E-3</v>
+      </c>
+      <c r="AK185">
+        <v>5.4115925597676201E-3</v>
+      </c>
+      <c r="AL185">
+        <v>3.3822453498547598E-4</v>
+      </c>
+      <c r="AM185">
+        <v>0.59375</v>
+      </c>
+    </row>
+    <row r="186" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>17</v>
+      </c>
+      <c r="B186" t="s">
+        <v>48</v>
+      </c>
+      <c r="C186" t="s">
+        <v>62</v>
+      </c>
+      <c r="D186">
+        <v>2027</v>
+      </c>
+      <c r="E186">
+        <v>7</v>
+      </c>
+      <c r="F186">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="G186">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="H186">
+        <v>0.42857142857142799</v>
+      </c>
+      <c r="I186">
+        <v>1</v>
+      </c>
+      <c r="J186">
+        <v>1.71428571428571</v>
+      </c>
+      <c r="K186">
+        <v>-0.71428571428571397</v>
+      </c>
+      <c r="L186">
+        <v>1.1428571428571399</v>
+      </c>
+      <c r="M186">
+        <v>90</v>
+      </c>
+      <c r="N186">
+        <v>650.59979454674703</v>
+      </c>
+      <c r="O186">
+        <v>0.52962117642763895</v>
+      </c>
+      <c r="P186">
+        <v>0.30801687763712998</v>
+      </c>
+      <c r="Q186">
+        <v>0.804953560371517</v>
+      </c>
+      <c r="R186">
+        <v>0.24458204334365299</v>
+      </c>
+      <c r="S186">
+        <v>4.8922056384742903E-2</v>
+      </c>
+      <c r="T186">
+        <v>0.25423728813559299</v>
+      </c>
+      <c r="U186">
+        <v>0.34745762711864397</v>
+      </c>
+      <c r="V186">
+        <v>2.9850746268656699E-2</v>
+      </c>
+      <c r="W186">
+        <v>0.102819237147595</v>
+      </c>
+      <c r="X186">
+        <v>5.3482587064676602E-2</v>
+      </c>
+      <c r="Y186">
+        <v>0.42635658914728602</v>
+      </c>
+      <c r="Z186">
+        <v>3.0679933665008201E-2</v>
+      </c>
+      <c r="AA186">
+        <v>4.4346962831945801E-2</v>
+      </c>
+      <c r="AB186">
+        <v>7.0021520260967099E-2</v>
+      </c>
+      <c r="AC186">
+        <v>0.65333333333333299</v>
+      </c>
+      <c r="AD186">
+        <v>2.8942228374532999E-2</v>
+      </c>
+      <c r="AE186">
+        <v>3.7344810805849102E-2</v>
+      </c>
+      <c r="AF186">
+        <v>8.08457711442786E-2</v>
+      </c>
+      <c r="AG186">
+        <v>7.9357722962429302E-3</v>
+      </c>
+      <c r="AH186">
+        <v>0.12697235673988699</v>
+      </c>
+      <c r="AI186">
+        <v>0.433823529411764</v>
+      </c>
+      <c r="AJ186">
+        <v>5.8684702694905702E-3</v>
+      </c>
+      <c r="AK186">
+        <v>8.4025824313160493E-3</v>
+      </c>
+      <c r="AL186">
+        <v>4.66810135073114E-4</v>
+      </c>
+      <c r="AM186">
+        <v>0.57142857142857095</v>
+      </c>
+    </row>
+    <row r="187" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>18</v>
+      </c>
+      <c r="B187" t="s">
+        <v>48</v>
+      </c>
+      <c r="C187" t="s">
+        <v>117</v>
+      </c>
+      <c r="D187">
+        <v>2027</v>
+      </c>
+      <c r="E187">
+        <v>7</v>
+      </c>
+      <c r="F187">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="G187">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="H187">
+        <v>0.42857142857142799</v>
+      </c>
+      <c r="I187">
+        <v>1.1428571428571399</v>
+      </c>
+      <c r="J187">
+        <v>2.5714285714285698</v>
+      </c>
+      <c r="K187">
+        <v>-1.4285714285714199</v>
+      </c>
+      <c r="L187">
+        <v>1.1428571428571399</v>
+      </c>
+      <c r="M187">
+        <v>90</v>
+      </c>
+      <c r="N187">
+        <v>671.60442401524301</v>
+      </c>
+      <c r="O187">
+        <v>0.35820405579396197</v>
+      </c>
+      <c r="P187">
+        <v>0.30916030534351102</v>
+      </c>
+      <c r="Q187">
+        <v>0.71379310344827496</v>
+      </c>
+      <c r="R187">
+        <v>0.451724137931034</v>
+      </c>
+      <c r="S187">
+        <v>3.9192399049881199E-2</v>
+      </c>
+      <c r="T187">
+        <v>0.37878787878787801</v>
+      </c>
+      <c r="U187">
+        <v>0.18181818181818099</v>
+      </c>
+      <c r="V187">
+        <v>2.3159144893111602E-2</v>
+      </c>
+      <c r="W187">
+        <v>0.10035629453681701</v>
+      </c>
+      <c r="X187">
+        <v>3.9192399049881199E-2</v>
+      </c>
+      <c r="Y187">
+        <v>0.30303030303030298</v>
+      </c>
+      <c r="Z187">
+        <v>4.75059382422802E-2</v>
+      </c>
+      <c r="AA187">
+        <v>3.5462979510362702E-2</v>
+      </c>
+      <c r="AB187">
+        <v>5.7668770418720601E-2</v>
+      </c>
+      <c r="AC187">
+        <v>0.77586206896551702</v>
+      </c>
+      <c r="AD187">
+        <v>2.5188658343809001E-2</v>
+      </c>
+      <c r="AE187">
+        <v>3.9771565806014202E-2</v>
+      </c>
+      <c r="AF187">
+        <v>0.14964370546318201</v>
+      </c>
+      <c r="AG187">
+        <v>3.31429715050118E-3</v>
+      </c>
+      <c r="AH187">
+        <v>0.118983267702992</v>
+      </c>
+      <c r="AI187">
+        <v>0.45403899721448399</v>
+      </c>
+      <c r="AJ187">
+        <v>5.8710406666021E-3</v>
+      </c>
+      <c r="AK187">
+        <v>3.9771565806014202E-3</v>
+      </c>
+      <c r="AL187">
+        <v>0</v>
+      </c>
+      <c r="AM187">
+        <v>0.67857142857142805</v>
+      </c>
+    </row>
+    <row r="188" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>19</v>
+      </c>
+      <c r="B188" t="s">
+        <v>48</v>
+      </c>
+      <c r="C188" t="s">
+        <v>118</v>
+      </c>
+      <c r="D188">
+        <v>2027</v>
+      </c>
+      <c r="E188">
+        <v>7</v>
+      </c>
+      <c r="F188">
+        <v>0.14285714285714199</v>
+      </c>
+      <c r="G188">
+        <v>0.57142857142857095</v>
+      </c>
+      <c r="H188">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="I188">
+        <v>1</v>
+      </c>
+      <c r="J188">
+        <v>1.28571428571428</v>
+      </c>
+      <c r="K188">
+        <v>-0.28571428571428498</v>
+      </c>
+      <c r="L188">
+        <v>1</v>
+      </c>
+      <c r="M188">
+        <v>90</v>
+      </c>
+      <c r="N188">
+        <v>790.31326933132402</v>
+      </c>
+      <c r="O188">
+        <v>0.452442648310797</v>
+      </c>
+      <c r="P188">
+        <v>0.25598086124401898</v>
+      </c>
+      <c r="Q188">
+        <v>0.83405275779376498</v>
+      </c>
+      <c r="R188">
+        <v>0.20047961630695399</v>
+      </c>
+      <c r="S188">
+        <v>3.4358769476627998E-2</v>
+      </c>
+      <c r="T188">
+        <v>0.27906976744186002</v>
+      </c>
+      <c r="U188">
+        <v>0.27906976744186002</v>
+      </c>
+      <c r="V188">
+        <v>2.0775069916100598E-2</v>
+      </c>
+      <c r="W188">
+        <v>7.5908909308829403E-2</v>
+      </c>
+      <c r="X188">
+        <v>3.1961646024770203E-2</v>
+      </c>
+      <c r="Y188">
+        <v>0.38750000000000001</v>
+      </c>
+      <c r="Z188">
+        <v>4.03515781062724E-2</v>
+      </c>
+      <c r="AA188">
+        <v>3.1691610153072702E-2</v>
+      </c>
+      <c r="AB188">
+        <v>5.8101285280633401E-2</v>
+      </c>
+      <c r="AC188">
+        <v>0.70454545454545403</v>
+      </c>
+      <c r="AD188">
+        <v>1.8816893528386901E-2</v>
+      </c>
+      <c r="AE188">
+        <v>3.6313303300395901E-2</v>
+      </c>
+      <c r="AF188">
+        <v>9.2688773471833796E-2</v>
+      </c>
+      <c r="AG188">
+        <v>2.64096751275606E-3</v>
+      </c>
+      <c r="AH188">
+        <v>9.4414588581029302E-2</v>
+      </c>
+      <c r="AI188">
+        <v>0.40559440559440502</v>
+      </c>
+      <c r="AJ188">
+        <v>3.8199708666650199E-3</v>
+      </c>
+      <c r="AK188">
+        <v>5.2819350255121304E-3</v>
+      </c>
+      <c r="AL188">
+        <v>0</v>
+      </c>
+      <c r="AM188">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="189" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>20</v>
+      </c>
+      <c r="B189" t="s">
+        <v>48</v>
+      </c>
+      <c r="C189" t="s">
+        <v>61</v>
+      </c>
+      <c r="D189">
+        <v>2027</v>
+      </c>
+      <c r="E189">
+        <v>7</v>
+      </c>
+      <c r="F189">
+        <v>0.14285714285714199</v>
+      </c>
+      <c r="G189">
+        <v>0.42857142857142799</v>
+      </c>
+      <c r="H189">
+        <v>0.42857142857142799</v>
+      </c>
+      <c r="I189">
+        <v>1.1428571428571399</v>
+      </c>
+      <c r="J189">
+        <v>1.28571428571428</v>
+      </c>
+      <c r="K189">
+        <v>-0.14285714285714199</v>
+      </c>
+      <c r="L189">
+        <v>0.85714285714285698</v>
+      </c>
+      <c r="M189">
+        <v>90</v>
+      </c>
+      <c r="N189">
+        <v>734.83485980632395</v>
+      </c>
+      <c r="O189">
+        <v>0.50098719764041399</v>
+      </c>
+      <c r="P189">
+        <v>0.31610337972166902</v>
+      </c>
+      <c r="Q189">
+        <v>0.82931533269045299</v>
+      </c>
+      <c r="R189">
+        <v>0.242526518804243</v>
+      </c>
+      <c r="S189">
+        <v>3.7252619324796198E-2</v>
+      </c>
+      <c r="T189">
+        <v>0.30208333333333298</v>
+      </c>
+      <c r="U189">
+        <v>0.36458333333333298</v>
+      </c>
+      <c r="V189">
+        <v>2.7939464493597198E-2</v>
+      </c>
+      <c r="W189">
+        <v>5.9759410166860601E-2</v>
+      </c>
+      <c r="X189">
+        <v>2.6775320139697301E-2</v>
+      </c>
+      <c r="Y189">
+        <v>0.46376811594202899</v>
+      </c>
+      <c r="Z189">
+        <v>3.0267753201396901E-2</v>
+      </c>
+      <c r="AA189">
+        <v>3.3893761899077397E-2</v>
+      </c>
+      <c r="AB189">
+        <v>4.9477100703251002E-2</v>
+      </c>
+      <c r="AC189">
+        <v>0.70866141732283405</v>
+      </c>
+      <c r="AD189">
+        <v>1.90895900351125E-2</v>
+      </c>
+      <c r="AE189">
+        <v>4.0127097420746799E-2</v>
+      </c>
+      <c r="AF189">
+        <v>8.9639115250291002E-2</v>
+      </c>
+      <c r="AG189">
+        <v>5.0645851113563997E-3</v>
+      </c>
+      <c r="AH189">
+        <v>0.11765420797150999</v>
+      </c>
+      <c r="AI189">
+        <v>0.50331125827814505</v>
+      </c>
+      <c r="AJ189">
+        <v>5.3428590185737798E-3</v>
+      </c>
+      <c r="AK189">
+        <v>5.8437520515650697E-3</v>
+      </c>
+      <c r="AL189">
+        <v>0</v>
+      </c>
+      <c r="AM189">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="190" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>21</v>
+      </c>
+      <c r="B190" t="s">
+        <v>48</v>
+      </c>
+      <c r="C190" t="s">
+        <v>87</v>
+      </c>
+      <c r="D190">
+        <v>2027</v>
+      </c>
+      <c r="E190">
+        <v>7</v>
+      </c>
+      <c r="F190">
+        <v>0</v>
+      </c>
+      <c r="G190">
+        <v>0.85714285714285698</v>
+      </c>
+      <c r="H190">
+        <v>0.14285714285714199</v>
+      </c>
+      <c r="I190">
+        <v>1.1428571428571399</v>
+      </c>
+      <c r="J190">
+        <v>1.4285714285714199</v>
+      </c>
+      <c r="K190">
+        <v>-0.28571428571428498</v>
+      </c>
+      <c r="L190">
+        <v>0.85714285714285698</v>
+      </c>
+      <c r="M190">
+        <v>90</v>
+      </c>
+      <c r="N190">
+        <v>701.18461555645501</v>
+      </c>
+      <c r="O190">
+        <v>0.43701553717830999</v>
+      </c>
+      <c r="P190">
+        <v>0.39915966386554602</v>
+      </c>
+      <c r="Q190">
+        <v>0.81845416417016104</v>
+      </c>
+      <c r="R190">
+        <v>0.28520071899340899</v>
+      </c>
+      <c r="S190">
+        <v>4.6620046620046603E-2</v>
+      </c>
+      <c r="T190">
+        <v>0.23</v>
+      </c>
+      <c r="U190">
+        <v>0.3</v>
+      </c>
+      <c r="V190">
+        <v>3.2167832167832103E-2</v>
+      </c>
+      <c r="W190">
+        <v>7.5524475524475498E-2</v>
+      </c>
+      <c r="X190">
+        <v>4.1025641025640998E-2</v>
+      </c>
+      <c r="Y190">
+        <v>0.38636363636363602</v>
+      </c>
+      <c r="Z190">
+        <v>3.03030303030303E-2</v>
+      </c>
+      <c r="AA190">
+        <v>3.1484182733741997E-2</v>
+      </c>
+      <c r="AB190">
+        <v>5.1387976415992603E-2</v>
+      </c>
+      <c r="AC190">
+        <v>0.68309859154929498</v>
+      </c>
+      <c r="AD190">
+        <v>2.24370037872644E-2</v>
+      </c>
+      <c r="AE190">
+        <v>3.5826828628051199E-2</v>
+      </c>
+      <c r="AF190">
+        <v>0.104428904428904</v>
+      </c>
+      <c r="AG190">
+        <v>6.1520816836047503E-3</v>
+      </c>
+      <c r="AH190">
+        <v>0.116527664830631</v>
+      </c>
+      <c r="AI190">
+        <v>0.453416149068323</v>
+      </c>
+      <c r="AJ190">
+        <v>5.94528902197098E-3</v>
+      </c>
+      <c r="AK190">
+        <v>4.3426458943092404E-3</v>
+      </c>
+      <c r="AL190">
+        <v>0</v>
+      </c>
+      <c r="AM190">
+        <v>0.71428571428571397</v>
+      </c>
+    </row>
+    <row r="191" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>22</v>
+      </c>
+      <c r="B191" t="s">
+        <v>48</v>
+      </c>
+      <c r="C191" t="s">
+        <v>65</v>
+      </c>
+      <c r="D191">
+        <v>2027</v>
+      </c>
+      <c r="E191">
+        <v>8</v>
+      </c>
+      <c r="F191">
+        <v>0.125</v>
+      </c>
+      <c r="G191">
+        <v>0.25</v>
+      </c>
+      <c r="H191">
+        <v>0.625</v>
+      </c>
+      <c r="I191">
+        <v>0.5</v>
+      </c>
+      <c r="J191">
+        <v>1.625</v>
+      </c>
+      <c r="K191">
+        <v>-1.125</v>
+      </c>
+      <c r="L191">
+        <v>0.625</v>
+      </c>
+      <c r="M191">
+        <v>90</v>
+      </c>
+      <c r="N191">
+        <v>848.12205871265303</v>
+      </c>
+      <c r="O191">
+        <v>0.57391503380872699</v>
+      </c>
+      <c r="P191">
+        <v>0.32193158953722301</v>
+      </c>
+      <c r="Q191">
+        <v>0.87665587282896595</v>
+      </c>
+      <c r="R191">
+        <v>0.14630556373270501</v>
+      </c>
+      <c r="S191">
+        <v>2.74781715459681E-2</v>
+      </c>
+      <c r="T191">
+        <v>0.21495327102803699</v>
+      </c>
+      <c r="U191">
+        <v>0.401869158878504</v>
+      </c>
+      <c r="V191">
+        <v>2.1058038007190499E-2</v>
+      </c>
+      <c r="W191">
+        <v>6.0092449922958299E-2</v>
+      </c>
+      <c r="X191">
+        <v>2.9019003595274699E-2</v>
+      </c>
+      <c r="Y191">
+        <v>0.42477876106194601</v>
+      </c>
+      <c r="Z191">
+        <v>2.4653312788906E-2</v>
+      </c>
+      <c r="AA191">
+        <v>2.5942791574416001E-2</v>
+      </c>
+      <c r="AB191">
+        <v>5.2923294811808699E-2</v>
+      </c>
+      <c r="AC191">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="AD191">
+        <v>1.69492904952851E-2</v>
+      </c>
+      <c r="AE191">
+        <v>3.2860869327593599E-2</v>
+      </c>
+      <c r="AF191">
+        <v>6.1890087313816101E-2</v>
+      </c>
+      <c r="AG191">
+        <v>4.4967505395654399E-3</v>
+      </c>
+      <c r="AH191">
+        <v>0.105500685735958</v>
+      </c>
+      <c r="AI191">
+        <v>0.44262295081967201</v>
+      </c>
+      <c r="AJ191">
+        <v>4.4535125536080897E-3</v>
+      </c>
+      <c r="AK191">
+        <v>4.1508466519065597E-3</v>
+      </c>
+      <c r="AL191">
+        <v>3.4590388765887999E-4</v>
+      </c>
+      <c r="AM191">
+        <v>0.65789473684210498</v>
+      </c>
+    </row>
+    <row r="192" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>23</v>
+      </c>
+      <c r="B192" t="s">
+        <v>48</v>
+      </c>
+      <c r="C192" t="s">
+        <v>63</v>
+      </c>
+      <c r="D192">
+        <v>2027</v>
+      </c>
+      <c r="E192">
+        <v>7</v>
+      </c>
+      <c r="F192">
+        <v>0.14285714285714199</v>
+      </c>
+      <c r="G192">
+        <v>0.14285714285714199</v>
+      </c>
+      <c r="H192">
+        <v>0.71428571428571397</v>
+      </c>
+      <c r="I192">
+        <v>0.71428571428571397</v>
+      </c>
+      <c r="J192">
+        <v>1.71428571428571</v>
+      </c>
+      <c r="K192">
+        <v>-1</v>
+      </c>
+      <c r="L192">
+        <v>0.57142857142857095</v>
+      </c>
+      <c r="M192">
+        <v>90</v>
+      </c>
+      <c r="N192">
+        <v>812.80572632492101</v>
+      </c>
+      <c r="O192">
+        <v>0.53694081782847503</v>
+      </c>
+      <c r="P192">
+        <v>0.37096774193548299</v>
+      </c>
+      <c r="Q192">
+        <v>0.86768542676108795</v>
+      </c>
+      <c r="R192">
+        <v>0.13865076407006999</v>
+      </c>
+      <c r="S192">
+        <v>3.2733224222585899E-2</v>
+      </c>
+      <c r="T192">
+        <v>0.22</v>
+      </c>
+      <c r="U192">
+        <v>0.27</v>
+      </c>
+      <c r="V192">
+        <v>2.38952536824877E-2</v>
+      </c>
+      <c r="W192">
+        <v>5.3027823240589099E-2</v>
+      </c>
+      <c r="X192">
+        <v>2.5859247135842801E-2</v>
+      </c>
+      <c r="Y192">
+        <v>0.379746835443038</v>
+      </c>
+      <c r="Z192">
+        <v>2.3567921440261801E-2</v>
+      </c>
+      <c r="AA192">
+        <v>2.8846444891515201E-2</v>
+      </c>
+      <c r="AB192">
+        <v>4.1751433395614101E-2</v>
+      </c>
+      <c r="AC192">
+        <v>0.75454545454545396</v>
+      </c>
+      <c r="AD192">
+        <v>1.8598365785318999E-2</v>
+      </c>
+      <c r="AE192">
+        <v>3.0364678833173901E-2</v>
+      </c>
+      <c r="AF192">
+        <v>6.8085106382978697E-2</v>
+      </c>
+      <c r="AG192">
+        <v>6.83205273746414E-3</v>
+      </c>
+      <c r="AH192">
+        <v>9.7166972266156601E-2</v>
+      </c>
+      <c r="AI192">
+        <v>0.453125</v>
+      </c>
+      <c r="AJ192">
+        <v>5.2053735142583903E-3</v>
+      </c>
+      <c r="AK192">
+        <v>6.4524942520494599E-3</v>
+      </c>
+      <c r="AL192">
+        <v>0</v>
+      </c>
+      <c r="AM192">
+        <v>0.53846153846153799</v>
       </c>
     </row>
   </sheetData>
